--- a/2026/ITALIA/Abril/Abril ITALIA.xlsx
+++ b/2026/ITALIA/Abril/Abril ITALIA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistemax\Desktop\rc-consorcio2025\2026\ITALIA\Abril\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\ITALIA\Abril\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{003B0629-4D99-4B59-9BD3-E506A2E04E34}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB4B4D96-9B6A-4D93-A989-A4C31886C146}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RESUMEN" sheetId="4" r:id="rId1"/>
@@ -22,16 +22,11 @@
     <definedName name="_xlnm.Print_Area" localSheetId="0">RESUMEN!$A$1:$E$140</definedName>
   </definedNames>
   <calcPr calcId="181029"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="256">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="278">
   <si>
     <t>TOTAL</t>
   </si>
@@ -809,6 +804,72 @@
   </si>
   <si>
     <t>Saldo inicial</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ANOTACION </t>
+  </si>
+  <si>
+    <t>FECHA DE LA ANOTACION:</t>
+  </si>
+  <si>
+    <t>0-ene</t>
+  </si>
+  <si>
+    <t>NOMBRE:</t>
+  </si>
+  <si>
+    <t>Ferraro jose</t>
+  </si>
+  <si>
+    <t>QUEJA VIA:</t>
+  </si>
+  <si>
+    <t>WHATSAPP</t>
+  </si>
+  <si>
+    <t>MAIL</t>
+  </si>
+  <si>
+    <t>MOTIVO DE LA QUEJA:</t>
+  </si>
+  <si>
+    <t>El 10 C habia abonado en el mes 4 $132.420,71 , le quedaban $3677 pesos a favor y la pusimos impaga - Debe abonar $130.084,71</t>
+  </si>
+  <si>
+    <t>El 10A deposito $220.300 el 08/05</t>
+  </si>
+  <si>
+    <t>10A</t>
+  </si>
+  <si>
+    <t>Cristina_Kruk@hotmail.com</t>
+  </si>
+  <si>
+    <t>Cristina</t>
+  </si>
+  <si>
+    <t>Deposito 15/05 $147.000</t>
+  </si>
+  <si>
+    <t>8C creo</t>
+  </si>
+  <si>
+    <t>Angelica</t>
+  </si>
+  <si>
+    <t>Deposito $160.000 el 19/05 (creo)</t>
+  </si>
+  <si>
+    <t>6F</t>
+  </si>
+  <si>
+    <t>Gustavo Peker</t>
+  </si>
+  <si>
+    <t>9B</t>
+  </si>
+  <si>
+    <t>Abono $180.866,63 el 27/04 y no lo pusimos pago. CHEQUEAR</t>
   </si>
 </sst>
 </file>
@@ -825,7 +886,7 @@
     <numFmt numFmtId="167" formatCode="_-&quot;$&quot;\ * #,##0_-;\-&quot;$&quot;\ * #,##0_-;_-&quot;$&quot;\ * &quot;-&quot;??_-;_-@_-"/>
     <numFmt numFmtId="168" formatCode="0.000"/>
   </numFmts>
-  <fonts count="21" x14ac:knownFonts="1">
+  <fonts count="22" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -981,8 +1042,16 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="15">
+  <fills count="19">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1067,6 +1136,30 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="40">
     <border>
@@ -1566,12 +1659,13 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="3">
+  <cellStyleXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="255">
+  <cellXfs count="290">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1874,9 +1968,6 @@
     <xf numFmtId="44" fontId="15" fillId="8" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="44" fontId="14" fillId="0" borderId="9" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
@@ -1913,18 +2004,50 @@
     <xf numFmtId="0" fontId="6" fillId="9" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="12" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="15" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="15" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="17" fillId="16" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="16" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="3"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="6" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
@@ -1949,12 +2072,81 @@
     <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="16" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1976,77 +2168,31 @@
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="18" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
-  <cellStyles count="3">
+  <cellStyles count="4">
+    <cellStyle name="Hipervínculo" xfId="3" builtinId="8"/>
     <cellStyle name="Millares" xfId="2" builtinId="3"/>
     <cellStyle name="Moneda" xfId="1" builtinId="4"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2129,9 +2275,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -2169,9 +2315,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -2204,26 +2350,9 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -2256,26 +2385,9 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -2450,31 +2562,31 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E413A25D-5161-4141-BE0B-6E37A2A76CA5}">
   <dimension ref="A1:M141"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="37.5703125" customWidth="1"/>
-    <col min="2" max="2" width="24.7109375" customWidth="1"/>
-    <col min="3" max="3" width="15.85546875" hidden="1" customWidth="1"/>
-    <col min="4" max="4" width="21.7109375" customWidth="1"/>
-    <col min="5" max="5" width="16.7109375" customWidth="1"/>
-    <col min="6" max="6" width="15.5703125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="37.5546875" customWidth="1"/>
+    <col min="2" max="2" width="24.6640625" customWidth="1"/>
+    <col min="3" max="3" width="15.88671875" hidden="1" customWidth="1"/>
+    <col min="4" max="4" width="21.6640625" customWidth="1"/>
+    <col min="5" max="5" width="16.6640625" customWidth="1"/>
+    <col min="6" max="6" width="15.5546875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5546875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="12" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="22.7109375" customWidth="1"/>
+    <col min="10" max="10" width="22.6640625" customWidth="1"/>
     <col min="11" max="11" width="18" customWidth="1"/>
-    <col min="12" max="12" width="18.28515625" customWidth="1"/>
+    <col min="12" max="12" width="18.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2"/>
-      <c r="B1" s="213" t="s">
+      <c r="B1" s="236" t="s">
         <v>149</v>
       </c>
-      <c r="C1" s="213"/>
-      <c r="D1" s="213"/>
-      <c r="E1" s="214"/>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
+      <c r="C1" s="236"/>
+      <c r="D1" s="236"/>
+      <c r="E1" s="237"/>
+    </row>
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="3"/>
       <c r="B2" s="10" t="s">
         <v>151</v>
@@ -2483,16 +2595,16 @@
       <c r="D2" s="4"/>
       <c r="E2" s="5"/>
     </row>
-    <row r="3" spans="1:5" ht="51.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" ht="51.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3"/>
-      <c r="B3" s="215" t="s">
+      <c r="B3" s="240" t="s">
         <v>253</v>
       </c>
-      <c r="C3" s="215"/>
-      <c r="D3" s="215"/>
-      <c r="E3" s="216"/>
-    </row>
-    <row r="4" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C3" s="240"/>
+      <c r="D3" s="240"/>
+      <c r="E3" s="241"/>
+    </row>
+    <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="6" t="s">
         <v>102</v>
       </c>
@@ -2503,7 +2615,7 @@
       <c r="D4" s="8"/>
       <c r="E4" s="9"/>
     </row>
-    <row r="5" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A5" s="3" t="s">
         <v>150</v>
       </c>
@@ -2516,7 +2628,7 @@
       </c>
       <c r="E5" s="11"/>
     </row>
-    <row r="6" spans="1:5" ht="16.149999999999999" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" ht="16.2" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A6" s="93" t="s">
         <v>140</v>
       </c>
@@ -2527,57 +2639,57 @@
       </c>
       <c r="E6" s="9"/>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B8" s="217" t="s">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B8" s="242" t="s">
         <v>196</v>
       </c>
-      <c r="C8" s="217"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B9" s="217"/>
-      <c r="C9" s="217"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="B10" s="217"/>
-      <c r="C10" s="217"/>
-    </row>
-    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="218" t="s">
+      <c r="C8" s="242"/>
+    </row>
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B9" s="242"/>
+      <c r="C9" s="242"/>
+    </row>
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="B10" s="242"/>
+      <c r="C10" s="242"/>
+    </row>
+    <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="243" t="s">
         <v>105</v>
       </c>
-      <c r="B13" s="218"/>
-      <c r="C13" s="218"/>
-      <c r="D13" s="218"/>
-      <c r="E13" s="218"/>
-    </row>
-    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="218"/>
-      <c r="B14" s="218"/>
-      <c r="C14" s="218"/>
-      <c r="D14" s="218"/>
-      <c r="E14" s="218"/>
-    </row>
-    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="218"/>
-      <c r="B15" s="218"/>
-      <c r="C15" s="218"/>
-      <c r="D15" s="218"/>
-      <c r="E15" s="218"/>
-    </row>
-    <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="218"/>
-      <c r="B16" s="218"/>
-      <c r="C16" s="218"/>
-      <c r="D16" s="218"/>
-      <c r="E16" s="218"/>
-    </row>
-    <row r="17" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="18" spans="1:8" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B13" s="243"/>
+      <c r="C13" s="243"/>
+      <c r="D13" s="243"/>
+      <c r="E13" s="243"/>
+    </row>
+    <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="243"/>
+      <c r="B14" s="243"/>
+      <c r="C14" s="243"/>
+      <c r="D14" s="243"/>
+      <c r="E14" s="243"/>
+    </row>
+    <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="243"/>
+      <c r="B15" s="243"/>
+      <c r="C15" s="243"/>
+      <c r="D15" s="243"/>
+      <c r="E15" s="243"/>
+    </row>
+    <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="243"/>
+      <c r="B16" s="243"/>
+      <c r="C16" s="243"/>
+      <c r="D16" s="243"/>
+      <c r="E16" s="243"/>
+    </row>
+    <row r="17" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="18" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A18" s="1"/>
     </row>
-    <row r="19" spans="1:8" ht="15.75" hidden="1" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" s="12" t="s">
         <v>106</v>
       </c>
@@ -2586,7 +2698,7 @@
       <c r="D20" s="15"/>
       <c r="E20" s="16"/>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" s="17" t="s">
         <v>141</v>
       </c>
@@ -2595,11 +2707,11 @@
       <c r="D21" s="128"/>
       <c r="E21" s="175"/>
     </row>
-    <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="211" t="s">
+    <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="238" t="s">
         <v>168</v>
       </c>
-      <c r="B22" s="212"/>
+      <c r="B22" s="239"/>
       <c r="C22" s="21"/>
       <c r="D22" s="137">
         <v>2038208.3</v>
@@ -2607,11 +2719,11 @@
       <c r="E22" s="176"/>
       <c r="H22" s="22"/>
     </row>
-    <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="211" t="s">
+    <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="238" t="s">
         <v>169</v>
       </c>
-      <c r="B23" s="212"/>
+      <c r="B23" s="239"/>
       <c r="C23" s="21"/>
       <c r="D23" s="137">
         <v>-443310.3</v>
@@ -2619,11 +2731,11 @@
       <c r="E23" s="23"/>
       <c r="H23" s="22"/>
     </row>
-    <row r="24" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="211" t="s">
+    <row r="24" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="238" t="s">
         <v>1</v>
       </c>
-      <c r="B24" s="212"/>
+      <c r="B24" s="239"/>
       <c r="C24" s="21"/>
       <c r="D24" s="138">
         <v>0</v>
@@ -2631,7 +2743,7 @@
       <c r="E24" s="23"/>
       <c r="H24" s="22"/>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25" s="24" t="s">
         <v>107</v>
       </c>
@@ -2643,7 +2755,7 @@
         <v>1594898</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" s="24" t="s">
         <v>188</v>
       </c>
@@ -2652,7 +2764,7 @@
       <c r="D26" s="25"/>
       <c r="E26" s="178"/>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" s="21" t="s">
         <v>211</v>
       </c>
@@ -2661,11 +2773,11 @@
       <c r="D27" s="38">
         <v>336000</v>
       </c>
-      <c r="E27" s="192" t="s">
+      <c r="E27" s="191" t="s">
         <v>212</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" s="21" t="s">
         <v>213</v>
       </c>
@@ -2674,9 +2786,9 @@
       <c r="D28" s="38">
         <v>3990</v>
       </c>
-      <c r="E28" s="192"/>
-    </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="E28" s="191"/>
+    </row>
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29" s="21" t="s">
         <v>175</v>
       </c>
@@ -2687,11 +2799,11 @@
       <c r="D29" s="38">
         <v>168000</v>
       </c>
-      <c r="E29" s="192" t="s">
+      <c r="E29" s="191" t="s">
         <v>203</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" s="21" t="s">
         <v>186</v>
       </c>
@@ -2704,7 +2816,7 @@
         <v>166</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31" s="24" t="s">
         <v>107</v>
       </c>
@@ -2716,7 +2828,7 @@
         <v>341842.51</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32" s="17" t="s">
         <v>142</v>
       </c>
@@ -2725,7 +2837,7 @@
       <c r="D32" s="25"/>
       <c r="E32" s="178"/>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" s="21" t="s">
         <v>243</v>
       </c>
@@ -2738,7 +2850,7 @@
         <v>244</v>
       </c>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" s="21" t="s">
         <v>154</v>
       </c>
@@ -2751,7 +2863,7 @@
         <v>228</v>
       </c>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" s="21" t="s">
         <v>144</v>
       </c>
@@ -2764,7 +2876,7 @@
         <v>223</v>
       </c>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" s="21" t="s">
         <v>146</v>
       </c>
@@ -2778,7 +2890,7 @@
         <v>Debito 13/04</v>
       </c>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" s="21" t="s">
         <v>145</v>
       </c>
@@ -2792,7 +2904,7 @@
         <v>Debito 13/04</v>
       </c>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" s="21" t="s">
         <v>155</v>
       </c>
@@ -2801,7 +2913,7 @@
       <c r="D38" s="38"/>
       <c r="E38" s="179"/>
     </row>
-    <row r="39" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:5" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A39" s="24" t="s">
         <v>143</v>
       </c>
@@ -2813,7 +2925,7 @@
         <v>1225378.4800000002</v>
       </c>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" s="17" t="s">
         <v>108</v>
       </c>
@@ -2822,11 +2934,11 @@
       <c r="D40" s="26"/>
       <c r="E40" s="180"/>
     </row>
-    <row r="41" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="219" t="s">
+    <row r="41" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A41" s="244" t="s">
         <v>215</v>
       </c>
-      <c r="B41" s="220"/>
+      <c r="B41" s="245"/>
       <c r="C41" s="29"/>
       <c r="D41" s="139">
         <v>7805</v>
@@ -2835,11 +2947,11 @@
         <v>216</v>
       </c>
     </row>
-    <row r="42" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="219" t="s">
+    <row r="42" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A42" s="244" t="s">
         <v>225</v>
       </c>
-      <c r="B42" s="220"/>
+      <c r="B42" s="245"/>
       <c r="C42" s="29"/>
       <c r="D42" s="139">
         <v>214164</v>
@@ -2848,7 +2960,7 @@
         <v>216</v>
       </c>
     </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A43" s="24" t="s">
         <v>109</v>
       </c>
@@ -2860,7 +2972,7 @@
         <v>221969</v>
       </c>
     </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A44" s="17" t="s">
         <v>110</v>
       </c>
@@ -2869,7 +2981,7 @@
       <c r="D44" s="31"/>
       <c r="E44" s="181"/>
     </row>
-    <row r="45" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A45" s="32" t="s">
         <v>111</v>
       </c>
@@ -2884,7 +2996,7 @@
         <v>200</v>
       </c>
     </row>
-    <row r="46" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A46" s="32" t="s">
         <v>111</v>
       </c>
@@ -2899,7 +3011,7 @@
         <v>201</v>
       </c>
     </row>
-    <row r="47" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="32" t="s">
         <v>190</v>
       </c>
@@ -2912,7 +3024,7 @@
       </c>
       <c r="E47" s="23"/>
     </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48" s="32" t="s">
         <v>191</v>
       </c>
@@ -2923,11 +3035,11 @@
       </c>
       <c r="E48" s="23"/>
     </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A49" s="219" t="s">
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A49" s="244" t="s">
         <v>112</v>
       </c>
-      <c r="B49" s="220"/>
+      <c r="B49" s="245"/>
       <c r="C49" s="32"/>
       <c r="D49" s="33">
         <v>4517309.87</v>
@@ -2936,7 +3048,7 @@
         <v>230</v>
       </c>
     </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50" s="35" t="s">
         <v>113</v>
       </c>
@@ -2945,7 +3057,7 @@
       <c r="D50" s="33"/>
       <c r="E50" s="23"/>
     </row>
-    <row r="51" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A51" s="24" t="s">
         <v>114</v>
       </c>
@@ -2957,18 +3069,18 @@
         <v>5518177.6600000001</v>
       </c>
     </row>
-    <row r="52" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A52" s="17"/>
       <c r="B52" s="24"/>
       <c r="C52" s="24"/>
       <c r="D52" s="25"/>
       <c r="E52" s="183"/>
     </row>
-    <row r="53" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="211" t="s">
+    <row r="53" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="238" t="s">
         <v>171</v>
       </c>
-      <c r="B53" s="212"/>
+      <c r="B53" s="239"/>
       <c r="C53" s="32"/>
       <c r="D53" s="33">
         <v>285000</v>
@@ -2977,11 +3089,11 @@
         <v>217</v>
       </c>
     </row>
-    <row r="54" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="211" t="s">
+    <row r="54" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="238" t="s">
         <v>226</v>
       </c>
-      <c r="B54" s="212"/>
+      <c r="B54" s="239"/>
       <c r="C54" s="32"/>
       <c r="D54" s="33">
         <v>470000</v>
@@ -2990,11 +3102,11 @@
         <v>227</v>
       </c>
     </row>
-    <row r="55" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="211" t="s">
+    <row r="55" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="238" t="s">
         <v>236</v>
       </c>
-      <c r="B55" s="212"/>
+      <c r="B55" s="239"/>
       <c r="C55" s="32"/>
       <c r="D55" s="33">
         <v>670000</v>
@@ -3003,11 +3115,11 @@
         <v>237</v>
       </c>
     </row>
-    <row r="56" spans="1:6" ht="33.6" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="211" t="s">
+    <row r="56" spans="1:6" ht="33.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A56" s="238" t="s">
         <v>204</v>
       </c>
-      <c r="B56" s="212"/>
+      <c r="B56" s="239"/>
       <c r="C56" s="32"/>
       <c r="D56" s="33">
         <v>35000</v>
@@ -3016,11 +3128,11 @@
         <v>203</v>
       </c>
     </row>
-    <row r="57" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="211" t="s">
+    <row r="57" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A57" s="238" t="s">
         <v>202</v>
       </c>
-      <c r="B57" s="212"/>
+      <c r="B57" s="239"/>
       <c r="C57" s="32"/>
       <c r="D57" s="33">
         <f>710000-380000</f>
@@ -3031,11 +3143,11 @@
       </c>
       <c r="F57" s="53"/>
     </row>
-    <row r="58" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="211" t="s">
+    <row r="58" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="238" t="s">
         <v>209</v>
       </c>
-      <c r="B58" s="212"/>
+      <c r="B58" s="239"/>
       <c r="C58" s="32"/>
       <c r="D58" s="33">
         <v>35000</v>
@@ -3045,11 +3157,11 @@
       </c>
       <c r="F58" s="53"/>
     </row>
-    <row r="59" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="211" t="s">
+    <row r="59" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="238" t="s">
         <v>221</v>
       </c>
-      <c r="B59" s="212"/>
+      <c r="B59" s="239"/>
       <c r="C59" s="32"/>
       <c r="D59" s="33">
         <v>35000</v>
@@ -3059,11 +3171,11 @@
       </c>
       <c r="F59" s="53"/>
     </row>
-    <row r="60" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="211" t="s">
+    <row r="60" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A60" s="238" t="s">
         <v>239</v>
       </c>
-      <c r="B60" s="212"/>
+      <c r="B60" s="239"/>
       <c r="C60" s="32"/>
       <c r="D60" s="33">
         <v>320000</v>
@@ -3073,63 +3185,63 @@
       </c>
       <c r="F60" s="53"/>
     </row>
-    <row r="61" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="211" t="s">
+    <row r="61" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="238" t="s">
         <v>205</v>
       </c>
-      <c r="B61" s="212"/>
+      <c r="B61" s="239"/>
       <c r="C61" s="32"/>
       <c r="D61" s="33">
         <v>105000</v>
       </c>
-      <c r="E61" s="191" t="s">
+      <c r="E61" s="190" t="s">
         <v>203</v>
       </c>
       <c r="F61" s="53"/>
     </row>
-    <row r="62" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="211" t="s">
+    <row r="62" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="238" t="s">
         <v>207</v>
       </c>
-      <c r="B62" s="212"/>
+      <c r="B62" s="239"/>
       <c r="C62" s="32"/>
       <c r="D62" s="33">
         <v>150000</v>
       </c>
-      <c r="E62" s="191" t="s">
+      <c r="E62" s="190" t="s">
         <v>208</v>
       </c>
       <c r="F62" s="53"/>
     </row>
-    <row r="63" spans="1:6" ht="93.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="211" t="s">
+    <row r="63" spans="1:6" ht="93.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A63" s="238" t="s">
         <v>218</v>
       </c>
-      <c r="B63" s="212"/>
+      <c r="B63" s="239"/>
       <c r="C63" s="32"/>
       <c r="D63" s="33">
         <v>2800000</v>
       </c>
-      <c r="E63" s="191" t="s">
+      <c r="E63" s="190" t="s">
         <v>203</v>
       </c>
       <c r="F63" s="53"/>
     </row>
-    <row r="64" spans="1:6" ht="31.9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="211" t="s">
+    <row r="64" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="238" t="s">
         <v>234</v>
       </c>
-      <c r="B64" s="212"/>
+      <c r="B64" s="239"/>
       <c r="C64" s="32"/>
       <c r="D64" s="33">
         <v>200000</v>
       </c>
-      <c r="E64" s="191" t="s">
+      <c r="E64" s="190" t="s">
         <v>206</v>
       </c>
       <c r="F64" s="53"/>
     </row>
-    <row r="65" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A65" s="19" t="s">
         <v>176</v>
       </c>
@@ -3143,7 +3255,7 @@
       </c>
       <c r="F65" s="53"/>
     </row>
-    <row r="66" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="102" t="s">
         <v>231</v>
       </c>
@@ -3157,11 +3269,11 @@
       </c>
       <c r="F66" s="53"/>
     </row>
-    <row r="67" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="102" t="s">
         <v>232</v>
       </c>
-      <c r="B67" s="190"/>
+      <c r="B67" s="20"/>
       <c r="C67" s="32"/>
       <c r="D67" s="33">
         <v>31400</v>
@@ -3171,11 +3283,11 @@
       </c>
       <c r="F67" s="53"/>
     </row>
-    <row r="68" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="102" t="s">
         <v>233</v>
       </c>
-      <c r="B68" s="190"/>
+      <c r="B68" s="20"/>
       <c r="C68" s="32"/>
       <c r="D68" s="33">
         <v>31400</v>
@@ -3185,7 +3297,7 @@
       </c>
       <c r="F68" s="53"/>
     </row>
-    <row r="69" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="102" t="s">
         <v>198</v>
       </c>
@@ -3194,24 +3306,24 @@
       <c r="D69" s="33">
         <v>141400</v>
       </c>
-      <c r="E69" s="191" t="s">
+      <c r="E69" s="190" t="s">
         <v>224</v>
       </c>
       <c r="F69" s="53"/>
     </row>
-    <row r="70" spans="1:6" ht="21.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="211" t="s">
+    <row r="70" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A70" s="238" t="s">
         <v>235</v>
       </c>
-      <c r="B70" s="212"/>
+      <c r="B70" s="239"/>
       <c r="C70" s="32"/>
       <c r="D70" s="33">
         <v>0</v>
       </c>
-      <c r="E70" s="191"/>
+      <c r="E70" s="190"/>
       <c r="F70" s="53"/>
     </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A71" s="24" t="s">
         <v>0</v>
       </c>
@@ -3223,7 +3335,7 @@
         <v>5674600</v>
       </c>
     </row>
-    <row r="72" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A72" s="17" t="s">
         <v>115</v>
       </c>
@@ -3232,11 +3344,11 @@
       <c r="D72" s="18"/>
       <c r="E72" s="175"/>
     </row>
-    <row r="73" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="211" t="s">
+    <row r="73" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A73" s="238" t="s">
         <v>220</v>
       </c>
-      <c r="B73" s="212"/>
+      <c r="B73" s="239"/>
       <c r="C73" s="21"/>
       <c r="D73" s="140">
         <v>650000</v>
@@ -3245,7 +3357,7 @@
         <v>203</v>
       </c>
     </row>
-    <row r="74" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="19" t="s">
         <v>189</v>
       </c>
@@ -3258,7 +3370,7 @@
         <v>229</v>
       </c>
     </row>
-    <row r="75" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A75" s="19" t="s">
         <v>170</v>
       </c>
@@ -3271,7 +3383,7 @@
         <v>222</v>
       </c>
     </row>
-    <row r="76" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="102" t="s">
         <v>199</v>
       </c>
@@ -3284,7 +3396,7 @@
         <v>214</v>
       </c>
     </row>
-    <row r="77" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A77" s="24" t="s">
         <v>107</v>
       </c>
@@ -3296,7 +3408,7 @@
         <v>1045000</v>
       </c>
     </row>
-    <row r="78" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A78" s="17" t="s">
         <v>116</v>
       </c>
@@ -3305,7 +3417,7 @@
       <c r="D78" s="41"/>
       <c r="E78" s="44"/>
     </row>
-    <row r="79" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A79" s="32" t="s">
         <v>152</v>
       </c>
@@ -3316,7 +3428,7 @@
       </c>
       <c r="E79" s="184"/>
     </row>
-    <row r="80" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A80" s="32" t="s">
         <v>153</v>
       </c>
@@ -3327,7 +3439,7 @@
       </c>
       <c r="E80" s="184"/>
     </row>
-    <row r="81" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A81" s="42" t="s">
         <v>107</v>
       </c>
@@ -3339,14 +3451,14 @@
         <v>254716.26</v>
       </c>
     </row>
-    <row r="82" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A82" s="32"/>
       <c r="B82" s="32"/>
       <c r="C82" s="32"/>
       <c r="D82" s="45"/>
       <c r="E82" s="46"/>
     </row>
-    <row r="83" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A83" s="47" t="s">
         <v>117</v>
       </c>
@@ -3355,13 +3467,13 @@
       <c r="D83" s="48"/>
       <c r="E83" s="49"/>
     </row>
-    <row r="84" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A84" s="50"/>
       <c r="D84" s="51"/>
       <c r="E84" s="52"/>
       <c r="F84" s="53"/>
     </row>
-    <row r="85" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A85" s="54" t="s">
         <v>118</v>
       </c>
@@ -3375,16 +3487,16 @@
       <c r="F85" s="59"/>
       <c r="G85" s="53"/>
     </row>
-    <row r="86" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:8" x14ac:dyDescent="0.3">
       <c r="D86" s="51"/>
       <c r="E86" s="51"/>
     </row>
-    <row r="87" spans="1:8" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:8" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D87" s="51"/>
       <c r="E87" s="51"/>
       <c r="H87" s="60"/>
     </row>
-    <row r="88" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A88" s="12" t="s">
         <v>119</v>
       </c>
@@ -3393,32 +3505,32 @@
       <c r="D88" s="61"/>
       <c r="E88" s="62"/>
     </row>
-    <row r="89" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A89" s="27"/>
       <c r="B89" s="28"/>
       <c r="C89" s="32"/>
       <c r="D89" s="38"/>
       <c r="E89" s="63"/>
     </row>
-    <row r="90" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="211"/>
-      <c r="B90" s="212"/>
+    <row r="90" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A90" s="238"/>
+      <c r="B90" s="239"/>
       <c r="C90" s="32"/>
       <c r="D90" s="38"/>
       <c r="E90" s="63"/>
     </row>
-    <row r="91" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:8" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D91" s="45"/>
       <c r="E91" s="45"/>
     </row>
-    <row r="92" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A92" s="27"/>
       <c r="B92" s="64"/>
       <c r="C92" s="32"/>
       <c r="D92" s="38"/>
       <c r="E92" s="63"/>
     </row>
-    <row r="93" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A93" s="65" t="s">
         <v>148</v>
       </c>
@@ -3430,15 +3542,15 @@
         <v>0</v>
       </c>
     </row>
-    <row r="94" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D94" s="51"/>
       <c r="E94" s="51"/>
     </row>
-    <row r="95" spans="1:8" hidden="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:8" hidden="1" x14ac:dyDescent="0.3">
       <c r="D95" s="51"/>
       <c r="E95" s="51"/>
     </row>
-    <row r="96" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A96" s="47" t="s">
         <v>120</v>
       </c>
@@ -3449,11 +3561,11 @@
         <v>3000000</v>
       </c>
     </row>
-    <row r="97" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D97" s="51"/>
       <c r="E97" s="51"/>
     </row>
-    <row r="98" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A98" s="54" t="s">
         <v>121</v>
       </c>
@@ -3465,11 +3577,11 @@
         <v>3000000</v>
       </c>
     </row>
-    <row r="99" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="D99" s="51"/>
       <c r="E99" s="51"/>
     </row>
-    <row r="100" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A100" s="67" t="s">
         <v>122</v>
       </c>
@@ -3480,7 +3592,7 @@
       <c r="D100" s="51"/>
       <c r="E100" s="51"/>
     </row>
-    <row r="101" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A101" s="67" t="s">
         <v>123</v>
       </c>
@@ -3491,7 +3603,7 @@
       <c r="D101" s="51"/>
       <c r="E101" s="51"/>
     </row>
-    <row r="102" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A102" s="67" t="s">
         <v>124</v>
       </c>
@@ -3502,7 +3614,7 @@
       <c r="D102" s="51"/>
       <c r="E102" s="51"/>
     </row>
-    <row r="103" spans="1:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A103" s="67" t="s">
         <v>125</v>
       </c>
@@ -3513,143 +3625,143 @@
       <c r="D103" s="51"/>
       <c r="E103" s="51"/>
     </row>
-    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D104" s="51"/>
       <c r="E104" s="51"/>
     </row>
-    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D105" s="51"/>
       <c r="E105" s="51"/>
     </row>
-    <row r="106" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A106" s="221" t="s">
+    <row r="106" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A106" s="246" t="s">
         <v>182</v>
       </c>
-      <c r="B106" s="221"/>
+      <c r="B106" s="246"/>
       <c r="D106" s="51"/>
       <c r="E106" s="51"/>
     </row>
-    <row r="107" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="221"/>
-      <c r="B107" s="221"/>
+    <row r="107" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A107" s="246"/>
+      <c r="B107" s="246"/>
       <c r="D107" s="51"/>
       <c r="E107" s="51"/>
     </row>
-    <row r="108" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A108" s="221"/>
-      <c r="B108" s="221"/>
+    <row r="108" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A108" s="246"/>
+      <c r="B108" s="246"/>
       <c r="D108" s="51"/>
       <c r="E108" s="51"/>
     </row>
-    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D109" s="51"/>
       <c r="E109" s="51"/>
     </row>
-    <row r="110" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A110" s="221" t="s">
+    <row r="110" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A110" s="246" t="s">
         <v>183</v>
       </c>
-      <c r="B110" s="221"/>
+      <c r="B110" s="246"/>
       <c r="D110" s="51"/>
       <c r="E110" s="51"/>
     </row>
-    <row r="111" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A111" s="221"/>
-      <c r="B111" s="221"/>
+    <row r="111" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A111" s="246"/>
+      <c r="B111" s="246"/>
       <c r="D111" s="51"/>
       <c r="E111" s="51"/>
     </row>
-    <row r="112" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A112" s="221"/>
-      <c r="B112" s="221"/>
+    <row r="112" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A112" s="246"/>
+      <c r="B112" s="246"/>
       <c r="D112" s="51"/>
       <c r="E112" s="51"/>
     </row>
-    <row r="113" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D113" s="51"/>
       <c r="E113" s="51"/>
     </row>
-    <row r="114" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A114" s="221" t="s">
+    <row r="114" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A114" s="246" t="s">
         <v>192</v>
       </c>
-      <c r="B114" s="221"/>
+      <c r="B114" s="246"/>
       <c r="D114" s="51"/>
       <c r="E114" s="51"/>
     </row>
-    <row r="115" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A115" s="221"/>
-      <c r="B115" s="221"/>
+    <row r="115" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A115" s="246"/>
+      <c r="B115" s="246"/>
       <c r="D115" s="51"/>
       <c r="E115" s="51"/>
     </row>
-    <row r="116" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A116" s="221"/>
-      <c r="B116" s="221"/>
+    <row r="116" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A116" s="246"/>
+      <c r="B116" s="246"/>
       <c r="D116" s="51"/>
       <c r="E116" s="51"/>
     </row>
-    <row r="117" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D117" s="51"/>
       <c r="E117" s="51"/>
     </row>
-    <row r="118" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A118" s="221" t="s">
+    <row r="118" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A118" s="246" t="s">
         <v>195</v>
       </c>
-      <c r="B118" s="221"/>
+      <c r="B118" s="246"/>
       <c r="D118" s="51"/>
       <c r="E118" s="51"/>
     </row>
-    <row r="119" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A119" s="221"/>
-      <c r="B119" s="221"/>
+    <row r="119" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A119" s="246"/>
+      <c r="B119" s="246"/>
       <c r="D119" s="51"/>
       <c r="E119" s="51"/>
     </row>
-    <row r="120" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A120" s="221"/>
-      <c r="B120" s="221"/>
+    <row r="120" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A120" s="246"/>
+      <c r="B120" s="246"/>
       <c r="D120" s="51"/>
       <c r="E120" s="51"/>
     </row>
-    <row r="121" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="D121" s="51"/>
       <c r="E121" s="51"/>
     </row>
-    <row r="122" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A122" s="221" t="s">
+    <row r="122" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A122" s="246" t="s">
         <v>194</v>
       </c>
-      <c r="B122" s="221"/>
+      <c r="B122" s="246"/>
       <c r="D122" s="51"/>
       <c r="E122" s="51"/>
     </row>
-    <row r="123" spans="1:5" ht="14.45" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A123" s="221"/>
-      <c r="B123" s="221"/>
+    <row r="123" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A123" s="246"/>
+      <c r="B123" s="246"/>
       <c r="D123" s="51"/>
       <c r="E123" s="51"/>
     </row>
-    <row r="124" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A124" s="221"/>
-      <c r="B124" s="221"/>
+    <row r="124" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A124" s="246"/>
+      <c r="B124" s="246"/>
       <c r="D124" s="51"/>
       <c r="E124" s="51"/>
     </row>
-    <row r="125" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:5" x14ac:dyDescent="0.3">
       <c r="D125" s="51"/>
       <c r="E125" s="51"/>
     </row>
-    <row r="126" spans="1:5" s="71" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:5" s="71" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A126"/>
       <c r="B126" s="69"/>
       <c r="C126" s="70"/>
       <c r="D126" s="186"/>
       <c r="E126" s="186"/>
     </row>
-    <row r="127" spans="1:5" s="71" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A127" s="210" t="s">
+    <row r="127" spans="1:5" s="71" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A127" s="209" t="s">
         <v>255</v>
       </c>
       <c r="B127" s="72">
@@ -3659,7 +3771,7 @@
       <c r="D127" s="187"/>
       <c r="E127" s="187"/>
     </row>
-    <row r="128" spans="1:5" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A128" s="29" t="s">
         <v>147</v>
       </c>
@@ -3670,7 +3782,7 @@
       <c r="D128" s="51"/>
       <c r="E128" s="51"/>
     </row>
-    <row r="129" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A129" s="29" t="s">
         <v>126</v>
       </c>
@@ -3682,19 +3794,19 @@
       <c r="E129" s="51"/>
       <c r="F129" s="69"/>
     </row>
-    <row r="130" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A130" s="29" t="s">
         <v>2</v>
       </c>
       <c r="B130" s="74">
         <f>PRORRATEO!F117</f>
-        <v>16408430.059999995</v>
+        <v>16721537.399999997</v>
       </c>
       <c r="D130" s="51"/>
       <c r="E130" s="51"/>
       <c r="F130" s="69"/>
     </row>
-    <row r="131" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A131" s="29" t="s">
         <v>246</v>
       </c>
@@ -3705,7 +3817,7 @@
       <c r="E131" s="51"/>
       <c r="F131" s="69"/>
     </row>
-    <row r="132" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A132" s="29" t="s">
         <v>247</v>
       </c>
@@ -3716,7 +3828,7 @@
       <c r="E132" s="51"/>
       <c r="F132" s="69"/>
     </row>
-    <row r="133" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A133" s="29" t="s">
         <v>240</v>
       </c>
@@ -3727,32 +3839,32 @@
       <c r="E133" s="51"/>
       <c r="F133" s="69"/>
     </row>
-    <row r="134" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:13" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A134" s="75" t="s">
         <v>167</v>
       </c>
       <c r="B134" s="76">
         <f>SUM(B127:C133)</f>
-        <v>-846287.21625497041</v>
+        <v>-533179.87625496869</v>
       </c>
       <c r="D134" s="69"/>
       <c r="E134" s="53"/>
       <c r="F134" s="53"/>
     </row>
-    <row r="135" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="136" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A136" s="222" t="s">
+    <row r="135" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="136" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A136" s="247" t="s">
         <v>127</v>
       </c>
-      <c r="B136" s="222"/>
-      <c r="C136" s="222"/>
-    </row>
-    <row r="137" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A137" s="222"/>
-      <c r="B137" s="222"/>
-      <c r="C137" s="222"/>
-    </row>
-    <row r="138" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B136" s="247"/>
+      <c r="C136" s="247"/>
+    </row>
+    <row r="137" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="A137" s="247"/>
+      <c r="B137" s="247"/>
+      <c r="C137" s="247"/>
+    </row>
+    <row r="138" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A138" s="77" t="s">
         <v>248</v>
       </c>
@@ -3762,7 +3874,7 @@
       <c r="C138" s="78"/>
       <c r="D138" s="59"/>
     </row>
-    <row r="139" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A139" s="168" t="s">
         <v>250</v>
       </c>
@@ -3772,7 +3884,7 @@
       <c r="C139" s="78"/>
       <c r="D139" s="59"/>
     </row>
-    <row r="140" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A140" s="79" t="s">
         <v>0</v>
       </c>
@@ -3782,7 +3894,7 @@
       </c>
       <c r="C140" s="81"/>
     </row>
-    <row r="141" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:13" x14ac:dyDescent="0.3">
       <c r="M141" s="82"/>
     </row>
   </sheetData>
@@ -3828,53 +3940,53 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{533DB7A7-09F4-49CF-B824-70F15C1FF525}">
   <dimension ref="A1:P125"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="4.28515625" customWidth="1"/>
-    <col min="2" max="2" width="25.5703125" customWidth="1"/>
-    <col min="3" max="3" width="0.140625" customWidth="1"/>
-    <col min="4" max="4" width="8.42578125" customWidth="1"/>
-    <col min="5" max="5" width="14.140625" customWidth="1"/>
-    <col min="6" max="6" width="12.28515625" customWidth="1"/>
-    <col min="7" max="7" width="10.5703125" customWidth="1"/>
-    <col min="8" max="8" width="9.5703125" customWidth="1"/>
-    <col min="9" max="9" width="12.42578125" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" customWidth="1"/>
-    <col min="11" max="12" width="12.28515625" customWidth="1"/>
-    <col min="13" max="13" width="14.7109375" customWidth="1"/>
-    <col min="14" max="14" width="14.28515625" customWidth="1"/>
-    <col min="15" max="15" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="4.33203125" customWidth="1"/>
+    <col min="2" max="2" width="25.5546875" customWidth="1"/>
+    <col min="3" max="3" width="0.109375" customWidth="1"/>
+    <col min="4" max="4" width="8.44140625" customWidth="1"/>
+    <col min="5" max="5" width="14.109375" customWidth="1"/>
+    <col min="6" max="6" width="12.33203125" customWidth="1"/>
+    <col min="7" max="7" width="10.5546875" customWidth="1"/>
+    <col min="8" max="8" width="9.5546875" customWidth="1"/>
+    <col min="9" max="9" width="12.44140625" customWidth="1"/>
+    <col min="10" max="10" width="14.44140625" customWidth="1"/>
+    <col min="11" max="12" width="12.33203125" customWidth="1"/>
+    <col min="13" max="13" width="14.6640625" customWidth="1"/>
+    <col min="14" max="14" width="14.33203125" customWidth="1"/>
+    <col min="15" max="15" width="7.33203125" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="12" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="103"/>
       <c r="B1" s="104"/>
       <c r="C1" s="104"/>
-      <c r="D1" s="232"/>
-      <c r="E1" s="232"/>
-      <c r="F1" s="232"/>
-      <c r="G1" s="232"/>
-      <c r="H1" s="232"/>
-      <c r="I1" s="232"/>
-      <c r="J1" s="232"/>
-      <c r="K1" s="232"/>
-      <c r="L1" s="232"/>
-      <c r="M1" s="232"/>
+      <c r="D1" s="248"/>
+      <c r="E1" s="248"/>
+      <c r="F1" s="248"/>
+      <c r="G1" s="248"/>
+      <c r="H1" s="248"/>
+      <c r="I1" s="248"/>
+      <c r="J1" s="248"/>
+      <c r="K1" s="248"/>
+      <c r="L1" s="248"/>
+      <c r="M1" s="248"/>
       <c r="N1" s="105"/>
     </row>
-    <row r="2" spans="1:16" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A2" s="106"/>
       <c r="B2" s="107"/>
       <c r="C2" s="108"/>
       <c r="D2" s="108" t="s">
         <v>128</v>
       </c>
-      <c r="E2" s="254">
+      <c r="E2" s="272">
         <v>3000000</v>
       </c>
-      <c r="F2" s="254"/>
+      <c r="F2" s="272"/>
       <c r="G2" s="108"/>
       <c r="H2" s="108"/>
       <c r="I2" s="108" t="s">
@@ -3893,7 +4005,7 @@
         <v>12678356.25</v>
       </c>
     </row>
-    <row r="3" spans="1:16" ht="12.95" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:16" ht="12.9" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="112"/>
       <c r="B3" s="113"/>
       <c r="C3" s="113"/>
@@ -3910,192 +4022,192 @@
       <c r="N3" s="116"/>
       <c r="O3" s="83"/>
     </row>
-    <row r="4" spans="1:16" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="233" t="s">
+    <row r="4" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="249" t="s">
         <v>165</v>
       </c>
-      <c r="B4" s="234"/>
-      <c r="C4" s="234"/>
-      <c r="D4" s="234"/>
-      <c r="E4" s="234"/>
-      <c r="F4" s="234"/>
-      <c r="G4" s="234"/>
-      <c r="H4" s="234"/>
-      <c r="I4" s="234"/>
-      <c r="J4" s="234"/>
-      <c r="K4" s="234"/>
-      <c r="L4" s="234"/>
-      <c r="M4" s="234"/>
-      <c r="N4" s="235"/>
+      <c r="B4" s="250"/>
+      <c r="C4" s="250"/>
+      <c r="D4" s="250"/>
+      <c r="E4" s="250"/>
+      <c r="F4" s="250"/>
+      <c r="G4" s="250"/>
+      <c r="H4" s="250"/>
+      <c r="I4" s="250"/>
+      <c r="J4" s="250"/>
+      <c r="K4" s="250"/>
+      <c r="L4" s="250"/>
+      <c r="M4" s="250"/>
+      <c r="N4" s="251"/>
       <c r="O4" s="83"/>
     </row>
-    <row r="5" spans="1:16" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="236"/>
-      <c r="B5" s="237"/>
-      <c r="C5" s="237"/>
-      <c r="D5" s="237"/>
-      <c r="E5" s="237"/>
-      <c r="F5" s="237"/>
-      <c r="G5" s="237"/>
-      <c r="H5" s="237"/>
-      <c r="I5" s="237"/>
-      <c r="J5" s="237"/>
-      <c r="K5" s="237"/>
-      <c r="L5" s="237"/>
-      <c r="M5" s="237"/>
-      <c r="N5" s="238"/>
+    <row r="5" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="252"/>
+      <c r="B5" s="253"/>
+      <c r="C5" s="253"/>
+      <c r="D5" s="253"/>
+      <c r="E5" s="253"/>
+      <c r="F5" s="253"/>
+      <c r="G5" s="253"/>
+      <c r="H5" s="253"/>
+      <c r="I5" s="253"/>
+      <c r="J5" s="253"/>
+      <c r="K5" s="253"/>
+      <c r="L5" s="253"/>
+      <c r="M5" s="253"/>
+      <c r="N5" s="254"/>
       <c r="O5" s="83"/>
     </row>
-    <row r="6" spans="1:16" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="236"/>
-      <c r="B6" s="237"/>
-      <c r="C6" s="237"/>
-      <c r="D6" s="237"/>
-      <c r="E6" s="237"/>
-      <c r="F6" s="237"/>
-      <c r="G6" s="237"/>
-      <c r="H6" s="237"/>
-      <c r="I6" s="237"/>
-      <c r="J6" s="237"/>
-      <c r="K6" s="237"/>
-      <c r="L6" s="237"/>
-      <c r="M6" s="237"/>
-      <c r="N6" s="238"/>
+    <row r="6" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="252"/>
+      <c r="B6" s="253"/>
+      <c r="C6" s="253"/>
+      <c r="D6" s="253"/>
+      <c r="E6" s="253"/>
+      <c r="F6" s="253"/>
+      <c r="G6" s="253"/>
+      <c r="H6" s="253"/>
+      <c r="I6" s="253"/>
+      <c r="J6" s="253"/>
+      <c r="K6" s="253"/>
+      <c r="L6" s="253"/>
+      <c r="M6" s="253"/>
+      <c r="N6" s="254"/>
       <c r="O6" s="83"/>
     </row>
-    <row r="7" spans="1:16" ht="12.95" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="236"/>
-      <c r="B7" s="237"/>
-      <c r="C7" s="237"/>
-      <c r="D7" s="237"/>
-      <c r="E7" s="237"/>
-      <c r="F7" s="237"/>
-      <c r="G7" s="237"/>
-      <c r="H7" s="237"/>
-      <c r="I7" s="237"/>
-      <c r="J7" s="237"/>
-      <c r="K7" s="237"/>
-      <c r="L7" s="237"/>
-      <c r="M7" s="237"/>
-      <c r="N7" s="238"/>
+    <row r="7" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="252"/>
+      <c r="B7" s="253"/>
+      <c r="C7" s="253"/>
+      <c r="D7" s="253"/>
+      <c r="E7" s="253"/>
+      <c r="F7" s="253"/>
+      <c r="G7" s="253"/>
+      <c r="H7" s="253"/>
+      <c r="I7" s="253"/>
+      <c r="J7" s="253"/>
+      <c r="K7" s="253"/>
+      <c r="L7" s="253"/>
+      <c r="M7" s="253"/>
+      <c r="N7" s="254"/>
       <c r="O7" s="83"/>
     </row>
-    <row r="8" spans="1:16" ht="192" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="239"/>
-      <c r="B8" s="240"/>
-      <c r="C8" s="240"/>
-      <c r="D8" s="240"/>
-      <c r="E8" s="240"/>
-      <c r="F8" s="240"/>
-      <c r="G8" s="240"/>
-      <c r="H8" s="240"/>
-      <c r="I8" s="240"/>
-      <c r="J8" s="240"/>
-      <c r="K8" s="240"/>
-      <c r="L8" s="240"/>
-      <c r="M8" s="240"/>
-      <c r="N8" s="241"/>
-    </row>
-    <row r="9" spans="1:16" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="248" t="s">
+    <row r="8" spans="1:16" ht="192" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A8" s="255"/>
+      <c r="B8" s="256"/>
+      <c r="C8" s="256"/>
+      <c r="D8" s="256"/>
+      <c r="E8" s="256"/>
+      <c r="F8" s="256"/>
+      <c r="G8" s="256"/>
+      <c r="H8" s="256"/>
+      <c r="I8" s="256"/>
+      <c r="J8" s="256"/>
+      <c r="K8" s="256"/>
+      <c r="L8" s="256"/>
+      <c r="M8" s="256"/>
+      <c r="N8" s="257"/>
+    </row>
+    <row r="9" spans="1:16" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A9" s="266" t="s">
         <v>163</v>
       </c>
-      <c r="B9" s="249"/>
-      <c r="C9" s="249"/>
-      <c r="D9" s="249"/>
-      <c r="E9" s="249"/>
-      <c r="F9" s="249"/>
-      <c r="G9" s="249"/>
-      <c r="H9" s="249"/>
-      <c r="I9" s="249"/>
-      <c r="J9" s="249"/>
-      <c r="K9" s="249"/>
-      <c r="L9" s="249"/>
-      <c r="M9" s="249"/>
-      <c r="N9" s="250"/>
-    </row>
-    <row r="10" spans="1:16" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="251" t="s">
+      <c r="B9" s="267"/>
+      <c r="C9" s="267"/>
+      <c r="D9" s="267"/>
+      <c r="E9" s="267"/>
+      <c r="F9" s="267"/>
+      <c r="G9" s="267"/>
+      <c r="H9" s="267"/>
+      <c r="I9" s="267"/>
+      <c r="J9" s="267"/>
+      <c r="K9" s="267"/>
+      <c r="L9" s="267"/>
+      <c r="M9" s="267"/>
+      <c r="N9" s="268"/>
+    </row>
+    <row r="10" spans="1:16" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A10" s="269" t="s">
         <v>164</v>
       </c>
-      <c r="B10" s="252"/>
-      <c r="C10" s="252"/>
-      <c r="D10" s="252"/>
-      <c r="E10" s="252"/>
-      <c r="F10" s="252"/>
-      <c r="G10" s="252"/>
-      <c r="H10" s="252"/>
-      <c r="I10" s="252"/>
-      <c r="J10" s="252"/>
-      <c r="K10" s="252"/>
-      <c r="L10" s="252"/>
-      <c r="M10" s="252"/>
-      <c r="N10" s="253"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A11" s="242" t="s">
+      <c r="B10" s="270"/>
+      <c r="C10" s="270"/>
+      <c r="D10" s="270"/>
+      <c r="E10" s="270"/>
+      <c r="F10" s="270"/>
+      <c r="G10" s="270"/>
+      <c r="H10" s="270"/>
+      <c r="I10" s="270"/>
+      <c r="J10" s="270"/>
+      <c r="K10" s="270"/>
+      <c r="L10" s="270"/>
+      <c r="M10" s="270"/>
+      <c r="N10" s="271"/>
+    </row>
+    <row r="11" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A11" s="258" t="s">
         <v>130</v>
       </c>
-      <c r="B11" s="244" t="s">
+      <c r="B11" s="260" t="s">
         <v>131</v>
       </c>
-      <c r="C11" s="244" t="s">
+      <c r="C11" s="260" t="s">
         <v>132</v>
       </c>
-      <c r="D11" s="244" t="s">
+      <c r="D11" s="260" t="s">
         <v>133</v>
       </c>
-      <c r="E11" s="223" t="s">
+      <c r="E11" s="262" t="s">
         <v>134</v>
       </c>
-      <c r="F11" s="244" t="s">
+      <c r="F11" s="260" t="s">
         <v>135</v>
       </c>
-      <c r="G11" s="246" t="s">
+      <c r="G11" s="264" t="s">
         <v>136</v>
       </c>
-      <c r="H11" s="223" t="s">
+      <c r="H11" s="262" t="s">
         <v>137</v>
       </c>
-      <c r="I11" s="223" t="s">
+      <c r="I11" s="262" t="s">
         <v>129</v>
       </c>
-      <c r="J11" s="223" t="s">
+      <c r="J11" s="262" t="s">
         <v>128</v>
       </c>
-      <c r="K11" s="225" t="s">
+      <c r="K11" s="273" t="s">
         <v>185</v>
       </c>
-      <c r="L11" s="227" t="s">
+      <c r="L11" s="275" t="s">
         <v>193</v>
       </c>
       <c r="M11" s="164" t="s">
         <v>138</v>
       </c>
-      <c r="N11" s="229" t="s">
+      <c r="N11" s="277" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="12" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="243"/>
-      <c r="B12" s="245"/>
-      <c r="C12" s="245"/>
-      <c r="D12" s="245"/>
-      <c r="E12" s="224"/>
-      <c r="F12" s="245"/>
-      <c r="G12" s="247"/>
-      <c r="H12" s="224"/>
-      <c r="I12" s="224"/>
-      <c r="J12" s="224"/>
-      <c r="K12" s="226"/>
-      <c r="L12" s="228"/>
+    <row r="12" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="259"/>
+      <c r="B12" s="261"/>
+      <c r="C12" s="261"/>
+      <c r="D12" s="261"/>
+      <c r="E12" s="263"/>
+      <c r="F12" s="261"/>
+      <c r="G12" s="265"/>
+      <c r="H12" s="263"/>
+      <c r="I12" s="263"/>
+      <c r="J12" s="263"/>
+      <c r="K12" s="274"/>
+      <c r="L12" s="276"/>
       <c r="M12" s="165" t="str">
         <f>RESUMEN!B8</f>
         <v>VTO 15/05</v>
       </c>
-      <c r="N12" s="230"/>
-    </row>
-    <row r="13" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="N12" s="278"/>
+    </row>
+    <row r="13" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="148">
         <v>1</v>
       </c>
@@ -4143,7 +4255,7 @@
         <v>0.01</v>
       </c>
     </row>
-    <row r="14" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="149">
         <v>2</v>
       </c>
@@ -4194,7 +4306,7 @@
         <v>173</v>
       </c>
     </row>
-    <row r="15" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="148">
         <v>3</v>
       </c>
@@ -4243,7 +4355,7 @@
         <v>0.03</v>
       </c>
     </row>
-    <row r="16" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="150">
         <v>4</v>
       </c>
@@ -4292,7 +4404,7 @@
         <v>0.04</v>
       </c>
     </row>
-    <row r="17" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="148">
         <v>5</v>
       </c>
@@ -4341,7 +4453,7 @@
         <v>0.05</v>
       </c>
     </row>
-    <row r="18" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A18" s="148">
         <v>6</v>
       </c>
@@ -4389,7 +4501,7 @@
         <v>6.0000000000000005E-2</v>
       </c>
     </row>
-    <row r="19" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A19" s="148">
         <v>7</v>
       </c>
@@ -4438,7 +4550,7 @@
         <v>7.0000000000000007E-2</v>
       </c>
     </row>
-    <row r="20" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A20" s="148">
         <v>8</v>
       </c>
@@ -4486,7 +4598,7 @@
         <v>0.08</v>
       </c>
     </row>
-    <row r="21" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A21" s="148">
         <v>9</v>
       </c>
@@ -4534,7 +4646,7 @@
         <v>0.09</v>
       </c>
     </row>
-    <row r="22" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A22" s="148">
         <v>10</v>
       </c>
@@ -4583,7 +4695,7 @@
         <v>9.9999999999999992E-2</v>
       </c>
     </row>
-    <row r="23" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A23" s="148">
         <v>11</v>
       </c>
@@ -4632,7 +4744,7 @@
         <v>0.10999999999999999</v>
       </c>
     </row>
-    <row r="24" spans="1:16" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:16" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A24" s="148">
         <v>12</v>
       </c>
@@ -4680,7 +4792,7 @@
         <v>0.11999999999999998</v>
       </c>
     </row>
-    <row r="25" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A25" s="148">
         <v>13</v>
       </c>
@@ -4729,7 +4841,7 @@
         <v>0.12999999999999998</v>
       </c>
     </row>
-    <row r="26" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A26" s="148">
         <v>14</v>
       </c>
@@ -4778,7 +4890,7 @@
         <v>0.13999999999999999</v>
       </c>
     </row>
-    <row r="27" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A27" s="150">
         <v>15</v>
       </c>
@@ -4827,7 +4939,7 @@
         <v>0.15</v>
       </c>
     </row>
-    <row r="28" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A28" s="148">
         <v>16</v>
       </c>
@@ -4876,7 +4988,7 @@
         <v>0.16</v>
       </c>
     </row>
-    <row r="29" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A29" s="148">
         <v>17</v>
       </c>
@@ -4925,7 +5037,7 @@
         <v>0.17</v>
       </c>
     </row>
-    <row r="30" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A30" s="150">
         <v>18</v>
       </c>
@@ -4974,7 +5086,7 @@
         <v>0.18000000000000002</v>
       </c>
     </row>
-    <row r="31" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A31" s="150">
         <v>19</v>
       </c>
@@ -5026,7 +5138,7 @@
         <v>161</v>
       </c>
     </row>
-    <row r="32" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A32" s="151">
         <v>20</v>
       </c>
@@ -5076,7 +5188,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="33" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A33" s="150">
         <v>21</v>
       </c>
@@ -5125,7 +5237,7 @@
         <v>0.21000000000000005</v>
       </c>
     </row>
-    <row r="34" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A34" s="150">
         <f>A33+1</f>
         <v>22</v>
@@ -5174,7 +5286,7 @@
         <v>0.22000000000000006</v>
       </c>
     </row>
-    <row r="35" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A35" s="148">
         <f t="shared" ref="A35:A98" si="9">A34+1</f>
         <v>23</v>
@@ -5224,7 +5336,7 @@
         <v>0.23000000000000007</v>
       </c>
     </row>
-    <row r="36" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A36" s="148">
         <f t="shared" si="9"/>
         <v>24</v>
@@ -5274,7 +5386,7 @@
         <v>0.24000000000000007</v>
       </c>
     </row>
-    <row r="37" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A37" s="148">
         <f t="shared" si="9"/>
         <v>25</v>
@@ -5321,7 +5433,7 @@
         <v>0.25000000000000006</v>
       </c>
     </row>
-    <row r="38" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A38" s="148">
         <f t="shared" si="9"/>
         <v>26</v>
@@ -5371,7 +5483,7 @@
         <v>0.26000000000000006</v>
       </c>
     </row>
-    <row r="39" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A39" s="148">
         <f t="shared" si="9"/>
         <v>27</v>
@@ -5423,7 +5535,7 @@
         <v>0.27000000000000007</v>
       </c>
     </row>
-    <row r="40" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A40" s="148">
         <f t="shared" si="9"/>
         <v>28</v>
@@ -5470,7 +5582,7 @@
         <v>0.28000000000000008</v>
       </c>
     </row>
-    <row r="41" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A41" s="150">
         <f t="shared" si="9"/>
         <v>29</v>
@@ -5523,47 +5635,47 @@
         <v>156</v>
       </c>
     </row>
-    <row r="42" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A42" s="203">
+    <row r="42" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A42" s="202">
         <f t="shared" si="9"/>
         <v>30</v>
       </c>
-      <c r="B42" s="204" t="s">
+      <c r="B42" s="203" t="s">
         <v>31</v>
       </c>
-      <c r="C42" s="205"/>
-      <c r="D42" s="206">
+      <c r="C42" s="204"/>
+      <c r="D42" s="205">
         <v>0.82</v>
       </c>
-      <c r="E42" s="197">
+      <c r="E42" s="196">
         <v>128431.3</v>
       </c>
-      <c r="F42" s="197">
+      <c r="F42" s="196">
         <v>132300</v>
       </c>
-      <c r="G42" s="207">
+      <c r="G42" s="206">
         <f t="shared" si="0"/>
         <v>-3868.6999999999971</v>
       </c>
-      <c r="H42" s="207">
+      <c r="H42" s="206">
         <f t="shared" si="4"/>
         <v>0</v>
       </c>
-      <c r="I42" s="208">
+      <c r="I42" s="207">
         <f t="shared" si="1"/>
         <v>109160.64731249999</v>
       </c>
-      <c r="J42" s="208">
+      <c r="J42" s="207">
         <f t="shared" si="2"/>
         <v>24600</v>
       </c>
-      <c r="K42" s="208"/>
-      <c r="L42" s="209"/>
-      <c r="M42" s="201">
+      <c r="K42" s="207"/>
+      <c r="L42" s="208"/>
+      <c r="M42" s="200">
         <f t="shared" si="5"/>
         <v>129892.3</v>
       </c>
-      <c r="N42" s="202">
+      <c r="N42" s="201">
         <f t="shared" si="8"/>
         <v>133789.29999999999</v>
       </c>
@@ -5572,7 +5684,7 @@
         <v>0.3000000000000001</v>
       </c>
     </row>
-    <row r="43" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A43" s="148">
         <f t="shared" si="9"/>
         <v>31</v>
@@ -5622,7 +5734,7 @@
         <v>0.31000000000000011</v>
       </c>
     </row>
-    <row r="44" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A44" s="148">
         <f t="shared" si="9"/>
         <v>32</v>
@@ -5669,7 +5781,7 @@
         <v>0.32000000000000012</v>
       </c>
     </row>
-    <row r="45" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A45" s="151">
         <f t="shared" si="9"/>
         <v>33</v>
@@ -5721,7 +5833,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="46" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A46" s="148">
         <f t="shared" si="9"/>
         <v>34</v>
@@ -5771,48 +5883,48 @@
         <v>0.34000000000000014</v>
       </c>
     </row>
-    <row r="47" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A47" s="193">
+    <row r="47" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A47" s="192">
         <f t="shared" si="9"/>
         <v>35</v>
       </c>
-      <c r="B47" s="194" t="s">
+      <c r="B47" s="193" t="s">
         <v>36</v>
       </c>
-      <c r="C47" s="195"/>
-      <c r="D47" s="196">
+      <c r="C47" s="194"/>
+      <c r="D47" s="195">
         <v>1.1200000000000001</v>
       </c>
-      <c r="E47" s="197">
+      <c r="E47" s="196">
         <v>148450.35</v>
       </c>
-      <c r="F47" s="197">
+      <c r="F47" s="196">
         <f>73000+75000</f>
         <v>148000</v>
       </c>
-      <c r="G47" s="198">
+      <c r="G47" s="197">
         <f t="shared" si="0"/>
         <v>450.35000000000582</v>
       </c>
-      <c r="H47" s="198">
+      <c r="H47" s="197">
         <f t="shared" si="4"/>
         <v>13.510500000000174</v>
       </c>
-      <c r="I47" s="199">
+      <c r="I47" s="198">
         <f t="shared" si="10"/>
         <v>149097.46950000001</v>
       </c>
-      <c r="J47" s="199">
+      <c r="J47" s="198">
         <f t="shared" si="11"/>
         <v>33600.000000000007</v>
       </c>
-      <c r="K47" s="199"/>
-      <c r="L47" s="200"/>
-      <c r="M47" s="201">
+      <c r="K47" s="198"/>
+      <c r="L47" s="199"/>
+      <c r="M47" s="200">
         <f t="shared" si="5"/>
         <v>183161.35</v>
       </c>
-      <c r="N47" s="202">
+      <c r="N47" s="201">
         <f t="shared" si="8"/>
         <v>188656.35</v>
       </c>
@@ -5824,7 +5936,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="48" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A48" s="148">
         <f t="shared" si="9"/>
         <v>36</v>
@@ -5877,7 +5989,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="49" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A49" s="148">
         <f t="shared" si="9"/>
         <v>37</v>
@@ -5924,7 +6036,7 @@
         <v>0.37000000000000016</v>
       </c>
     </row>
-    <row r="50" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A50" s="148">
         <f t="shared" si="9"/>
         <v>38</v>
@@ -5977,7 +6089,7 @@
         <v>245</v>
       </c>
     </row>
-    <row r="51" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A51" s="148">
         <f t="shared" si="9"/>
         <v>39</v>
@@ -6024,7 +6136,7 @@
         <v>0.39000000000000018</v>
       </c>
     </row>
-    <row r="52" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A52" s="148">
         <f t="shared" si="9"/>
         <v>40</v>
@@ -6071,7 +6183,7 @@
         <v>0.40000000000000019</v>
       </c>
     </row>
-    <row r="53" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A53" s="148">
         <f t="shared" si="9"/>
         <v>41</v>
@@ -6121,7 +6233,7 @@
         <v>0.4100000000000002</v>
       </c>
     </row>
-    <row r="54" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A54" s="151">
         <f t="shared" si="9"/>
         <v>42</v>
@@ -6173,7 +6285,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="55" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A55" s="151">
         <f t="shared" si="9"/>
         <v>43</v>
@@ -6228,7 +6340,7 @@
         <v>241</v>
       </c>
     </row>
-    <row r="56" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A56" s="148">
         <f t="shared" si="9"/>
         <v>44</v>
@@ -6278,7 +6390,7 @@
         <v>0.44000000000000022</v>
       </c>
     </row>
-    <row r="57" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A57" s="148">
         <f t="shared" si="9"/>
         <v>45</v>
@@ -6328,12 +6440,12 @@
         <v>0.45000000000000023</v>
       </c>
     </row>
-    <row r="58" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A58" s="150">
+    <row r="58" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A58" s="231">
         <f t="shared" si="9"/>
         <v>46</v>
       </c>
-      <c r="B58" s="124" t="s">
+      <c r="B58" s="232" t="s">
         <v>46</v>
       </c>
       <c r="C58" s="90"/>
@@ -6380,7 +6492,7 @@
         <v>157</v>
       </c>
     </row>
-    <row r="59" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A59" s="151">
         <f t="shared" si="9"/>
         <v>47</v>
@@ -6431,7 +6543,7 @@
         <v>249</v>
       </c>
     </row>
-    <row r="60" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A60" s="150">
         <f t="shared" si="9"/>
         <v>48</v>
@@ -6484,7 +6596,7 @@
         <v>159</v>
       </c>
     </row>
-    <row r="61" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A61" s="150">
         <f t="shared" si="9"/>
         <v>49</v>
@@ -6534,7 +6646,7 @@
         <v>0.49000000000000027</v>
       </c>
     </row>
-    <row r="62" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A62" s="150">
         <f t="shared" si="9"/>
         <v>50</v>
@@ -6584,7 +6696,7 @@
         <v>0.50000000000000022</v>
       </c>
     </row>
-    <row r="63" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A63" s="150">
         <f t="shared" si="9"/>
         <v>51</v>
@@ -6634,7 +6746,7 @@
         <v>0.51000000000000023</v>
       </c>
     </row>
-    <row r="64" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A64" s="150">
         <f t="shared" si="9"/>
         <v>52</v>
@@ -6684,7 +6796,7 @@
         <v>0.52000000000000024</v>
       </c>
     </row>
-    <row r="65" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A65" s="150">
         <f t="shared" si="9"/>
         <v>53</v>
@@ -6734,7 +6846,7 @@
         <v>0.53000000000000025</v>
       </c>
     </row>
-    <row r="66" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A66" s="150">
         <f t="shared" si="9"/>
         <v>54</v>
@@ -6784,7 +6896,7 @@
         <v>0.54000000000000026</v>
       </c>
     </row>
-    <row r="67" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A67" s="150">
         <f t="shared" si="9"/>
         <v>55</v>
@@ -6833,7 +6945,7 @@
         <v>0.55000000000000027</v>
       </c>
     </row>
-    <row r="68" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A68" s="150">
         <f t="shared" si="9"/>
         <v>56</v>
@@ -6884,7 +6996,7 @@
         <v>0.56000000000000028</v>
       </c>
     </row>
-    <row r="69" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A69" s="150">
         <f t="shared" si="9"/>
         <v>57</v>
@@ -6933,7 +7045,7 @@
         <v>0.57000000000000028</v>
       </c>
     </row>
-    <row r="70" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A70" s="150">
         <f t="shared" si="9"/>
         <v>58</v>
@@ -6983,7 +7095,7 @@
         <v>0.58000000000000029</v>
       </c>
     </row>
-    <row r="71" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A71" s="150">
         <f t="shared" si="9"/>
         <v>59</v>
@@ -7032,7 +7144,7 @@
         <v>0.5900000000000003</v>
       </c>
     </row>
-    <row r="72" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A72" s="150">
         <f t="shared" si="9"/>
         <v>60</v>
@@ -7081,7 +7193,7 @@
         <v>0.60000000000000031</v>
       </c>
     </row>
-    <row r="73" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A73" s="148">
         <f t="shared" si="9"/>
         <v>61</v>
@@ -7131,7 +7243,7 @@
         <v>0.61000000000000032</v>
       </c>
     </row>
-    <row r="74" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A74" s="148">
         <f t="shared" si="9"/>
         <v>62</v>
@@ -7180,7 +7292,7 @@
         <v>0.62000000000000033</v>
       </c>
     </row>
-    <row r="75" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A75" s="148">
         <f t="shared" si="9"/>
         <v>63</v>
@@ -7195,14 +7307,17 @@
       <c r="E75" s="86">
         <v>180866.63</v>
       </c>
-      <c r="F75" s="87"/>
+      <c r="F75" s="87">
+        <f>E75</f>
+        <v>180866.63</v>
+      </c>
       <c r="G75" s="88">
         <f t="shared" si="0"/>
-        <v>180866.63</v>
+        <v>0</v>
       </c>
       <c r="H75" s="88">
         <f t="shared" si="4"/>
-        <v>5425.9988999999996</v>
+        <v>0</v>
       </c>
       <c r="I75" s="143">
         <f t="shared" si="10"/>
@@ -7216,18 +7331,21 @@
       <c r="L75" s="169"/>
       <c r="M75" s="89">
         <f t="shared" si="5"/>
-        <v>368990.63</v>
+        <v>182697.63</v>
       </c>
       <c r="N75" s="159">
         <f t="shared" si="8"/>
-        <v>380060.63</v>
+        <v>188178.63</v>
       </c>
       <c r="O75" s="53">
         <f t="shared" si="7"/>
         <v>0.63000000000000034</v>
       </c>
-    </row>
-    <row r="76" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="P75" t="s">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="76" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A76" s="148">
         <f t="shared" si="9"/>
         <v>64</v>
@@ -7278,7 +7396,7 @@
         <v>0.64000000000000035</v>
       </c>
     </row>
-    <row r="77" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A77" s="150">
         <f t="shared" si="9"/>
         <v>65</v>
@@ -7328,7 +7446,7 @@
         <v>180</v>
       </c>
     </row>
-    <row r="78" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A78" s="148">
         <f t="shared" si="9"/>
         <v>66</v>
@@ -7377,7 +7495,7 @@
         <v>0.66000000000000036</v>
       </c>
     </row>
-    <row r="79" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A79" s="148">
         <f t="shared" si="9"/>
         <v>67</v>
@@ -7427,7 +7545,7 @@
         <v>0.67000000000000037</v>
       </c>
     </row>
-    <row r="80" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A80" s="148">
         <f t="shared" si="9"/>
         <v>68</v>
@@ -7476,12 +7594,12 @@
         <v>0.68000000000000038</v>
       </c>
     </row>
-    <row r="81" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A81" s="148">
+    <row r="81" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A81" s="224">
         <f t="shared" si="9"/>
         <v>69</v>
       </c>
-      <c r="B81" s="91" t="s">
+      <c r="B81" s="225" t="s">
         <v>69</v>
       </c>
       <c r="C81" s="90"/>
@@ -7526,7 +7644,7 @@
         <v>0.69000000000000039</v>
       </c>
     </row>
-    <row r="82" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A82" s="150">
         <f t="shared" si="9"/>
         <v>70</v>
@@ -7579,12 +7697,12 @@
         <v>174</v>
       </c>
     </row>
-    <row r="83" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A83" s="150">
+    <row r="83" spans="1:16" x14ac:dyDescent="0.3">
+      <c r="A83" s="213">
         <f t="shared" si="9"/>
         <v>71</v>
       </c>
-      <c r="B83" s="124" t="s">
+      <c r="B83" s="214" t="s">
         <v>71</v>
       </c>
       <c r="C83" s="90"/>
@@ -7594,14 +7712,17 @@
       <c r="E83" s="86">
         <v>128563.71</v>
       </c>
-      <c r="F83" s="87"/>
+      <c r="F83" s="87">
+        <f>E83+3677</f>
+        <v>132240.71000000002</v>
+      </c>
       <c r="G83" s="88">
         <f t="shared" si="14"/>
-        <v>128563.71</v>
+        <v>-3677.0000000000146</v>
       </c>
       <c r="H83" s="88">
         <f t="shared" si="17"/>
-        <v>3856.9113000000002</v>
+        <v>0</v>
       </c>
       <c r="I83" s="143">
         <f t="shared" si="15"/>
@@ -7615,18 +7736,18 @@
       <c r="L83" s="169"/>
       <c r="M83" s="89">
         <f t="shared" si="18"/>
-        <v>266181.71000000002</v>
+        <v>130084.71</v>
       </c>
       <c r="N83" s="159">
         <f t="shared" si="8"/>
-        <v>274166.71000000002</v>
+        <v>133987.71000000002</v>
       </c>
       <c r="O83" s="53">
         <f t="shared" si="7"/>
         <v>0.71000000000000041</v>
       </c>
     </row>
-    <row r="84" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A84" s="148">
         <f t="shared" si="9"/>
         <v>72</v>
@@ -7676,7 +7797,7 @@
         <v>0.72000000000000042</v>
       </c>
     </row>
-    <row r="85" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A85" s="148">
         <f t="shared" si="9"/>
         <v>73</v>
@@ -7726,7 +7847,7 @@
         <v>0.73000000000000043</v>
       </c>
     </row>
-    <row r="86" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A86" s="148">
         <f t="shared" si="9"/>
         <v>74</v>
@@ -7773,7 +7894,7 @@
         <v>0.74000000000000044</v>
       </c>
     </row>
-    <row r="87" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A87" s="148">
         <f t="shared" si="9"/>
         <v>75</v>
@@ -7822,7 +7943,7 @@
         <v>0.75000000000000044</v>
       </c>
     </row>
-    <row r="88" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A88" s="148">
         <f t="shared" si="9"/>
         <v>76</v>
@@ -7872,7 +7993,7 @@
         <v>0.76000000000000045</v>
       </c>
     </row>
-    <row r="89" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A89" s="148">
         <f t="shared" si="9"/>
         <v>77</v>
@@ -7921,7 +8042,7 @@
         <v>0.77000000000000046</v>
       </c>
     </row>
-    <row r="90" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A90" s="151">
         <f t="shared" si="9"/>
         <v>78</v>
@@ -7973,7 +8094,7 @@
         <v>251</v>
       </c>
     </row>
-    <row r="91" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A91" s="148">
         <f t="shared" si="9"/>
         <v>79</v>
@@ -8023,7 +8144,7 @@
         <v>0.79000000000000048</v>
       </c>
     </row>
-    <row r="92" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A92" s="150">
         <f t="shared" si="9"/>
         <v>80</v>
@@ -8073,7 +8194,7 @@
         <v>0.80000000000000049</v>
       </c>
     </row>
-    <row r="93" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A93" s="149">
         <f t="shared" si="9"/>
         <v>81</v>
@@ -8123,7 +8244,7 @@
         <v>181</v>
       </c>
     </row>
-    <row r="94" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A94" s="148">
         <f t="shared" si="9"/>
         <v>82</v>
@@ -8173,7 +8294,7 @@
         <v>0.82000000000000051</v>
       </c>
     </row>
-    <row r="95" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A95" s="150">
         <f t="shared" si="9"/>
         <v>83</v>
@@ -8223,7 +8344,7 @@
         <v>0.83000000000000052</v>
       </c>
     </row>
-    <row r="96" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A96" s="150">
         <f t="shared" si="9"/>
         <v>84</v>
@@ -8273,7 +8394,7 @@
         <v>0.84000000000000052</v>
       </c>
     </row>
-    <row r="97" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A97" s="148">
         <f t="shared" si="9"/>
         <v>85</v>
@@ -8323,7 +8444,7 @@
         <v>0.85000000000000053</v>
       </c>
     </row>
-    <row r="98" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A98" s="148">
         <f t="shared" si="9"/>
         <v>86</v>
@@ -8373,7 +8494,7 @@
         <v>0.86000000000000054</v>
       </c>
     </row>
-    <row r="99" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A99" s="148">
         <f t="shared" ref="A99:A115" si="21">A98+1</f>
         <v>87</v>
@@ -8423,7 +8544,7 @@
         <v>0.87000000000000055</v>
       </c>
     </row>
-    <row r="100" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A100" s="148">
         <f t="shared" si="21"/>
         <v>88</v>
@@ -8473,7 +8594,7 @@
         <v>0.88000000000000056</v>
       </c>
     </row>
-    <row r="101" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A101" s="148">
         <f t="shared" si="21"/>
         <v>89</v>
@@ -8523,7 +8644,7 @@
         <v>0.89000000000000057</v>
       </c>
     </row>
-    <row r="102" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A102" s="148">
         <f t="shared" si="21"/>
         <v>90</v>
@@ -8573,7 +8694,7 @@
         <v>0.90000000000000058</v>
       </c>
     </row>
-    <row r="103" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A103" s="148">
         <f t="shared" si="21"/>
         <v>91</v>
@@ -8623,7 +8744,7 @@
         <v>0.91000000000000059</v>
       </c>
     </row>
-    <row r="104" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A104" s="148">
         <f t="shared" si="21"/>
         <v>92</v>
@@ -8673,7 +8794,7 @@
         <v>0.9200000000000006</v>
       </c>
     </row>
-    <row r="105" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A105" s="150">
         <f t="shared" si="21"/>
         <v>93</v>
@@ -8722,7 +8843,7 @@
         <v>0.9300000000000006</v>
       </c>
     </row>
-    <row r="106" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A106" s="150">
         <f t="shared" si="21"/>
         <v>94</v>
@@ -8772,7 +8893,7 @@
         <v>0.94000000000000061</v>
       </c>
     </row>
-    <row r="107" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:16" ht="24" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A107" s="150">
         <f t="shared" si="21"/>
         <v>95</v>
@@ -8822,7 +8943,7 @@
         <v>0.95000000000000062</v>
       </c>
     </row>
-    <row r="108" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A108" s="150">
         <f t="shared" si="21"/>
         <v>96</v>
@@ -8874,7 +8995,7 @@
         <v>160</v>
       </c>
     </row>
-    <row r="109" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A109" s="150">
         <f t="shared" si="21"/>
         <v>97</v>
@@ -8924,7 +9045,7 @@
         <v>0.97000000000000064</v>
       </c>
     </row>
-    <row r="110" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A110" s="150">
         <f t="shared" si="21"/>
         <v>98</v>
@@ -8974,7 +9095,7 @@
         <v>0.98000000000000065</v>
       </c>
     </row>
-    <row r="111" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A111" s="150">
         <f t="shared" si="21"/>
         <v>99</v>
@@ -9023,7 +9144,7 @@
         <v>0.99000000000000066</v>
       </c>
     </row>
-    <row r="112" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A112" s="150">
         <f t="shared" si="21"/>
         <v>100</v>
@@ -9073,7 +9194,7 @@
         <v>1.0000000000000007</v>
       </c>
     </row>
-    <row r="113" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A113" s="150">
         <f t="shared" si="21"/>
         <v>101</v>
@@ -9122,7 +9243,7 @@
         <v>1.0100000000000007</v>
       </c>
     </row>
-    <row r="114" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A114" s="150">
         <f t="shared" si="21"/>
         <v>102</v>
@@ -9172,7 +9293,7 @@
         <v>1.0200000000000007</v>
       </c>
     </row>
-    <row r="115" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A115" s="150">
         <f t="shared" si="21"/>
         <v>103</v>
@@ -9222,7 +9343,7 @@
         <v>1.0300000000000007</v>
       </c>
     </row>
-    <row r="116" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:15" x14ac:dyDescent="0.3">
       <c r="A116" s="150"/>
       <c r="B116" s="118"/>
       <c r="C116" s="123"/>
@@ -9239,7 +9360,7 @@
       <c r="N116" s="161"/>
       <c r="O116" s="53"/>
     </row>
-    <row r="117" spans="1:15" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:15" ht="17.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A117" s="152"/>
       <c r="B117" s="153"/>
       <c r="C117" s="153"/>
@@ -9253,15 +9374,15 @@
       </c>
       <c r="F117" s="156">
         <f>SUM(F13:F116)</f>
-        <v>16408430.059999995</v>
+        <v>16721537.399999997</v>
       </c>
       <c r="G117" s="156">
         <f t="shared" si="25"/>
-        <v>17899722.5</v>
+        <v>17586615.16</v>
       </c>
       <c r="H117" s="156">
         <f t="shared" si="25"/>
-        <v>539673.29219999991</v>
+        <v>530390.38199999987</v>
       </c>
       <c r="I117" s="157">
         <f t="shared" si="25"/>
@@ -9275,106 +9396,108 @@
       <c r="L117" s="173"/>
       <c r="M117" s="166">
         <f t="shared" si="25"/>
-        <v>36209119.560000002</v>
+        <v>35886729.56000001</v>
       </c>
       <c r="N117" s="163">
         <f t="shared" si="25"/>
-        <v>37295397.560000002</v>
-      </c>
-    </row>
-    <row r="118" spans="1:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.25">
+        <v>36963336.560000002</v>
+      </c>
+    </row>
+    <row r="118" spans="1:15" ht="12.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B118" s="92"/>
       <c r="C118" s="92"/>
     </row>
-    <row r="119" spans="1:15" hidden="1" x14ac:dyDescent="0.25"/>
-    <row r="120" spans="1:15" ht="9" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B120" s="231" t="s">
+    <row r="119" spans="1:15" hidden="1" x14ac:dyDescent="0.3"/>
+    <row r="120" spans="1:15" ht="9" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B120" s="279" t="s">
         <v>105</v>
       </c>
-      <c r="C120" s="231"/>
-      <c r="D120" s="231"/>
-      <c r="E120" s="231"/>
-      <c r="F120" s="231"/>
-      <c r="G120" s="231"/>
-      <c r="H120" s="231"/>
-      <c r="I120" s="231"/>
-      <c r="J120" s="231"/>
-      <c r="K120" s="231"/>
-      <c r="L120" s="231"/>
-      <c r="M120" s="231"/>
-    </row>
-    <row r="121" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B121" s="231"/>
-      <c r="C121" s="231"/>
-      <c r="D121" s="231"/>
-      <c r="E121" s="231"/>
-      <c r="F121" s="231"/>
-      <c r="G121" s="231"/>
-      <c r="H121" s="231"/>
-      <c r="I121" s="231"/>
-      <c r="J121" s="231"/>
-      <c r="K121" s="231"/>
-      <c r="L121" s="231"/>
-      <c r="M121" s="231"/>
-    </row>
-    <row r="122" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B122" s="231"/>
-      <c r="C122" s="231"/>
-      <c r="D122" s="231"/>
-      <c r="E122" s="231"/>
-      <c r="F122" s="231"/>
-      <c r="G122" s="231"/>
-      <c r="H122" s="231"/>
-      <c r="I122" s="231"/>
-      <c r="J122" s="231"/>
-      <c r="K122" s="231"/>
-      <c r="L122" s="231"/>
-      <c r="M122" s="231"/>
-    </row>
-    <row r="123" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B123" s="231"/>
-      <c r="C123" s="231"/>
-      <c r="D123" s="231"/>
-      <c r="E123" s="231"/>
-      <c r="F123" s="231"/>
-      <c r="G123" s="231"/>
-      <c r="H123" s="231"/>
-      <c r="I123" s="231"/>
-      <c r="J123" s="231"/>
-      <c r="K123" s="231"/>
-      <c r="L123" s="231"/>
-      <c r="M123" s="231"/>
-    </row>
-    <row r="124" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B124" s="231"/>
-      <c r="C124" s="231"/>
-      <c r="D124" s="231"/>
-      <c r="E124" s="231"/>
-      <c r="F124" s="231"/>
-      <c r="G124" s="231"/>
-      <c r="H124" s="231"/>
-      <c r="I124" s="231"/>
-      <c r="J124" s="231"/>
-      <c r="K124" s="231"/>
-      <c r="L124" s="231"/>
-      <c r="M124" s="231"/>
-    </row>
-    <row r="125" spans="1:15" ht="67.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="B125" s="231"/>
-      <c r="C125" s="231"/>
-      <c r="D125" s="231"/>
-      <c r="E125" s="231"/>
-      <c r="F125" s="231"/>
-      <c r="G125" s="231"/>
-      <c r="H125" s="231"/>
-      <c r="I125" s="231"/>
-      <c r="J125" s="231"/>
-      <c r="K125" s="231"/>
-      <c r="L125" s="231"/>
-      <c r="M125" s="231"/>
+      <c r="C120" s="279"/>
+      <c r="D120" s="279"/>
+      <c r="E120" s="279"/>
+      <c r="F120" s="279"/>
+      <c r="G120" s="279"/>
+      <c r="H120" s="279"/>
+      <c r="I120" s="279"/>
+      <c r="J120" s="279"/>
+      <c r="K120" s="279"/>
+      <c r="L120" s="279"/>
+      <c r="M120" s="279"/>
+    </row>
+    <row r="121" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B121" s="279"/>
+      <c r="C121" s="279"/>
+      <c r="D121" s="279"/>
+      <c r="E121" s="279"/>
+      <c r="F121" s="279"/>
+      <c r="G121" s="279"/>
+      <c r="H121" s="279"/>
+      <c r="I121" s="279"/>
+      <c r="J121" s="279"/>
+      <c r="K121" s="279"/>
+      <c r="L121" s="279"/>
+      <c r="M121" s="279"/>
+    </row>
+    <row r="122" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B122" s="279"/>
+      <c r="C122" s="279"/>
+      <c r="D122" s="279"/>
+      <c r="E122" s="279"/>
+      <c r="F122" s="279"/>
+      <c r="G122" s="279"/>
+      <c r="H122" s="279"/>
+      <c r="I122" s="279"/>
+      <c r="J122" s="279"/>
+      <c r="K122" s="279"/>
+      <c r="L122" s="279"/>
+      <c r="M122" s="279"/>
+    </row>
+    <row r="123" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B123" s="279"/>
+      <c r="C123" s="279"/>
+      <c r="D123" s="279"/>
+      <c r="E123" s="279"/>
+      <c r="F123" s="279"/>
+      <c r="G123" s="279"/>
+      <c r="H123" s="279"/>
+      <c r="I123" s="279"/>
+      <c r="J123" s="279"/>
+      <c r="K123" s="279"/>
+      <c r="L123" s="279"/>
+      <c r="M123" s="279"/>
+    </row>
+    <row r="124" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B124" s="279"/>
+      <c r="C124" s="279"/>
+      <c r="D124" s="279"/>
+      <c r="E124" s="279"/>
+      <c r="F124" s="279"/>
+      <c r="G124" s="279"/>
+      <c r="H124" s="279"/>
+      <c r="I124" s="279"/>
+      <c r="J124" s="279"/>
+      <c r="K124" s="279"/>
+      <c r="L124" s="279"/>
+      <c r="M124" s="279"/>
+    </row>
+    <row r="125" spans="1:15" ht="67.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B125" s="279"/>
+      <c r="C125" s="279"/>
+      <c r="D125" s="279"/>
+      <c r="E125" s="279"/>
+      <c r="F125" s="279"/>
+      <c r="G125" s="279"/>
+      <c r="H125" s="279"/>
+      <c r="I125" s="279"/>
+      <c r="J125" s="279"/>
+      <c r="K125" s="279"/>
+      <c r="L125" s="279"/>
+      <c r="M125" s="279"/>
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="J11:J12"/>
+    <mergeCell ref="N11:N12"/>
     <mergeCell ref="B120:M125"/>
     <mergeCell ref="D1:M1"/>
     <mergeCell ref="A4:N8"/>
@@ -9392,8 +9515,6 @@
     <mergeCell ref="I11:I12"/>
     <mergeCell ref="K11:K12"/>
     <mergeCell ref="L11:L12"/>
-    <mergeCell ref="J11:J12"/>
-    <mergeCell ref="N11:N12"/>
   </mergeCells>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="3" scale="80" orientation="portrait" r:id="rId1"/>
@@ -9402,26 +9523,425 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{56D35F41-74CB-4294-A7A2-EC3C67574818}">
-  <dimension ref="C3:I25"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="10.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A3:J41"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="3" width="12.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.6640625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="3:9" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C3" s="22"/>
     </row>
-    <row r="4" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C4" s="22"/>
-    </row>
-    <row r="5" spans="3:9" ht="18.75" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="14" spans="3:9" x14ac:dyDescent="0.25">
-      <c r="C14" s="22"/>
-      <c r="I14" s="69"/>
-    </row>
-    <row r="25" ht="117" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="4" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C4" s="215" t="s">
+        <v>256</v>
+      </c>
+      <c r="D4" s="216">
+        <v>1</v>
+      </c>
+      <c r="E4" s="210"/>
+      <c r="F4" s="210"/>
+      <c r="G4" s="210"/>
+      <c r="H4" s="210"/>
+      <c r="I4" s="210"/>
+      <c r="J4" s="211"/>
+    </row>
+    <row r="5" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="C5" s="217" t="s">
+        <v>257</v>
+      </c>
+      <c r="D5" s="218"/>
+      <c r="E5" t="s">
+        <v>258</v>
+      </c>
+      <c r="G5" t="s">
+        <v>259</v>
+      </c>
+      <c r="H5" t="s">
+        <v>260</v>
+      </c>
+      <c r="J5" s="212"/>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="C6" s="217" t="s">
+        <v>261</v>
+      </c>
+      <c r="D6" s="218" t="s">
+        <v>262</v>
+      </c>
+      <c r="E6" t="s">
+        <v>263</v>
+      </c>
+      <c r="G6" t="s">
+        <v>130</v>
+      </c>
+      <c r="H6">
+        <v>71</v>
+      </c>
+      <c r="J6" s="212"/>
+    </row>
+    <row r="7" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C7" s="50" t="s">
+        <v>264</v>
+      </c>
+      <c r="J7" s="212"/>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="C8" s="280" t="s">
+        <v>265</v>
+      </c>
+      <c r="D8" s="281"/>
+      <c r="E8" s="281"/>
+      <c r="F8" s="281"/>
+      <c r="G8" s="281"/>
+      <c r="H8" s="281"/>
+      <c r="I8" s="281"/>
+      <c r="J8" s="282"/>
+    </row>
+    <row r="9" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C9" s="283"/>
+      <c r="D9" s="284"/>
+      <c r="E9" s="284"/>
+      <c r="F9" s="284"/>
+      <c r="G9" s="284"/>
+      <c r="H9" s="284"/>
+      <c r="I9" s="284"/>
+      <c r="J9" s="285"/>
+    </row>
+    <row r="11" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A11" s="219"/>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="C12" s="220" t="s">
+        <v>256</v>
+      </c>
+      <c r="D12" s="221">
+        <f>D4+1</f>
+        <v>2</v>
+      </c>
+      <c r="E12" s="210"/>
+      <c r="F12" s="210"/>
+      <c r="G12" s="210"/>
+      <c r="H12" s="210"/>
+      <c r="I12" s="210"/>
+      <c r="J12" s="211"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="C13" s="222" t="s">
+        <v>257</v>
+      </c>
+      <c r="D13" s="223"/>
+      <c r="E13" t="s">
+        <v>258</v>
+      </c>
+      <c r="G13" t="s">
+        <v>259</v>
+      </c>
+      <c r="H13" t="s">
+        <v>260</v>
+      </c>
+      <c r="J13" s="212"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="C14" s="222" t="s">
+        <v>261</v>
+      </c>
+      <c r="D14" s="223" t="s">
+        <v>262</v>
+      </c>
+      <c r="E14" t="s">
+        <v>263</v>
+      </c>
+      <c r="G14" t="s">
+        <v>130</v>
+      </c>
+      <c r="H14" t="s">
+        <v>267</v>
+      </c>
+      <c r="J14" s="212"/>
+    </row>
+    <row r="15" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C15" s="50" t="s">
+        <v>264</v>
+      </c>
+      <c r="J15" s="212"/>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="C16" s="280" t="s">
+        <v>266</v>
+      </c>
+      <c r="D16" s="281"/>
+      <c r="E16" s="281"/>
+      <c r="F16" s="281"/>
+      <c r="G16" s="281"/>
+      <c r="H16" s="281"/>
+      <c r="I16" s="281"/>
+      <c r="J16" s="282"/>
+    </row>
+    <row r="17" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C17" s="283"/>
+      <c r="D17" s="284"/>
+      <c r="E17" s="284"/>
+      <c r="F17" s="284"/>
+      <c r="G17" s="284"/>
+      <c r="H17" s="284"/>
+      <c r="I17" s="284"/>
+      <c r="J17" s="285"/>
+    </row>
+    <row r="19" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="20" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C20" s="227" t="s">
+        <v>256</v>
+      </c>
+      <c r="D20" s="228">
+        <f>D12+1</f>
+        <v>3</v>
+      </c>
+      <c r="E20" s="210"/>
+      <c r="F20" s="210"/>
+      <c r="G20" s="210"/>
+      <c r="H20" s="210"/>
+      <c r="I20" s="210"/>
+      <c r="J20" s="211"/>
+    </row>
+    <row r="21" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C21" s="229" t="s">
+        <v>257</v>
+      </c>
+      <c r="D21" s="230"/>
+      <c r="E21" t="s">
+        <v>258</v>
+      </c>
+      <c r="G21" t="s">
+        <v>259</v>
+      </c>
+      <c r="H21" t="s">
+        <v>269</v>
+      </c>
+      <c r="I21" s="226" t="s">
+        <v>268</v>
+      </c>
+      <c r="J21" s="212"/>
+    </row>
+    <row r="22" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C22" s="229" t="s">
+        <v>261</v>
+      </c>
+      <c r="D22" s="230" t="s">
+        <v>262</v>
+      </c>
+      <c r="E22" t="s">
+        <v>263</v>
+      </c>
+      <c r="G22" t="s">
+        <v>130</v>
+      </c>
+      <c r="H22" t="s">
+        <v>271</v>
+      </c>
+      <c r="J22" s="212"/>
+    </row>
+    <row r="23" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C23" s="50" t="s">
+        <v>264</v>
+      </c>
+      <c r="J23" s="212"/>
+    </row>
+    <row r="24" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C24" s="280" t="s">
+        <v>270</v>
+      </c>
+      <c r="D24" s="281"/>
+      <c r="E24" s="281"/>
+      <c r="F24" s="281"/>
+      <c r="G24" s="281"/>
+      <c r="H24" s="281"/>
+      <c r="I24" s="281"/>
+      <c r="J24" s="282"/>
+    </row>
+    <row r="25" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C25" s="283"/>
+      <c r="D25" s="284"/>
+      <c r="E25" s="284"/>
+      <c r="F25" s="284"/>
+      <c r="G25" s="284"/>
+      <c r="H25" s="284"/>
+      <c r="I25" s="284"/>
+      <c r="J25" s="285"/>
+    </row>
+    <row r="27" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="28" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C28" s="233" t="s">
+        <v>256</v>
+      </c>
+      <c r="D28" s="15">
+        <f>D20+1</f>
+        <v>4</v>
+      </c>
+      <c r="E28" s="210"/>
+      <c r="F28" s="210"/>
+      <c r="G28" s="210"/>
+      <c r="H28" s="210"/>
+      <c r="I28" s="210"/>
+      <c r="J28" s="211"/>
+    </row>
+    <row r="29" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C29" s="234" t="s">
+        <v>257</v>
+      </c>
+      <c r="D29" s="235"/>
+      <c r="E29" t="s">
+        <v>258</v>
+      </c>
+      <c r="G29" t="s">
+        <v>259</v>
+      </c>
+      <c r="H29" t="s">
+        <v>272</v>
+      </c>
+      <c r="I29" s="226"/>
+      <c r="J29" s="212"/>
+    </row>
+    <row r="30" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C30" s="234" t="s">
+        <v>261</v>
+      </c>
+      <c r="D30" s="235" t="s">
+        <v>262</v>
+      </c>
+      <c r="E30" t="s">
+        <v>263</v>
+      </c>
+      <c r="G30" t="s">
+        <v>130</v>
+      </c>
+      <c r="H30">
+        <v>46</v>
+      </c>
+      <c r="I30" t="s">
+        <v>274</v>
+      </c>
+      <c r="J30" s="212"/>
+    </row>
+    <row r="31" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C31" s="50" t="s">
+        <v>264</v>
+      </c>
+      <c r="J31" s="212"/>
+    </row>
+    <row r="32" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C32" s="280" t="s">
+        <v>273</v>
+      </c>
+      <c r="D32" s="281"/>
+      <c r="E32" s="281"/>
+      <c r="F32" s="281"/>
+      <c r="G32" s="281"/>
+      <c r="H32" s="281"/>
+      <c r="I32" s="281"/>
+      <c r="J32" s="282"/>
+    </row>
+    <row r="33" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C33" s="283"/>
+      <c r="D33" s="284"/>
+      <c r="E33" s="284"/>
+      <c r="F33" s="284"/>
+      <c r="G33" s="284"/>
+      <c r="H33" s="284"/>
+      <c r="I33" s="284"/>
+      <c r="J33" s="285"/>
+    </row>
+    <row r="35" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
+    <row r="36" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C36" s="286" t="s">
+        <v>256</v>
+      </c>
+      <c r="D36" s="287">
+        <f>D28+1</f>
+        <v>5</v>
+      </c>
+      <c r="E36" s="210"/>
+      <c r="F36" s="210"/>
+      <c r="G36" s="210"/>
+      <c r="H36" s="210"/>
+      <c r="I36" s="210"/>
+      <c r="J36" s="211"/>
+    </row>
+    <row r="37" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C37" s="288" t="s">
+        <v>257</v>
+      </c>
+      <c r="D37" s="289"/>
+      <c r="E37" t="s">
+        <v>258</v>
+      </c>
+      <c r="G37" t="s">
+        <v>259</v>
+      </c>
+      <c r="H37" t="s">
+        <v>275</v>
+      </c>
+      <c r="I37" s="226"/>
+      <c r="J37" s="212"/>
+    </row>
+    <row r="38" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C38" s="288" t="s">
+        <v>261</v>
+      </c>
+      <c r="D38" s="289" t="s">
+        <v>262</v>
+      </c>
+      <c r="E38" t="s">
+        <v>263</v>
+      </c>
+      <c r="G38" t="s">
+        <v>130</v>
+      </c>
+      <c r="H38" t="s">
+        <v>276</v>
+      </c>
+      <c r="J38" s="212"/>
+    </row>
+    <row r="39" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C39" s="50" t="s">
+        <v>264</v>
+      </c>
+      <c r="J39" s="212"/>
+    </row>
+    <row r="40" spans="3:10" x14ac:dyDescent="0.3">
+      <c r="C40" s="280" t="s">
+        <v>277</v>
+      </c>
+      <c r="D40" s="281"/>
+      <c r="E40" s="281"/>
+      <c r="F40" s="281"/>
+      <c r="G40" s="281"/>
+      <c r="H40" s="281"/>
+      <c r="I40" s="281"/>
+      <c r="J40" s="282"/>
+    </row>
+    <row r="41" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C41" s="283"/>
+      <c r="D41" s="284"/>
+      <c r="E41" s="284"/>
+      <c r="F41" s="284"/>
+      <c r="G41" s="284"/>
+      <c r="H41" s="284"/>
+      <c r="I41" s="284"/>
+      <c r="J41" s="285"/>
+    </row>
   </sheetData>
+  <mergeCells count="5">
+    <mergeCell ref="C8:J9"/>
+    <mergeCell ref="C16:J17"/>
+    <mergeCell ref="C24:J25"/>
+    <mergeCell ref="C32:J33"/>
+    <mergeCell ref="C40:J41"/>
+  </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="I21" r:id="rId1" xr:uid="{594C449D-3B6C-4B8F-B1F1-8C5EBB24B131}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/2026/ITALIA/Abril/Abril ITALIA.xlsx
+++ b/2026/ITALIA/Abril/Abril ITALIA.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Sistema\Desktop\rc-consorcio2025\2026\ITALIA\Abril\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB4B4D96-9B6A-4D93-A989-A4C31886C146}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6FC41BD7-F22B-4A95-A0A6-DDDFF4D8F812}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -587,9 +587,6 @@
     <t xml:space="preserve">Plan de pago de 4G: Consta de 7 cuotas de $170.000 + expensas en curso </t>
   </si>
   <si>
-    <t xml:space="preserve">Plan de pago de 11C: Consta de 11 cuotas de 250.000 + expensas en curso </t>
-  </si>
-  <si>
     <t>10 A 15HS - EMERGENCIAS 24HS</t>
   </si>
   <si>
@@ -870,6 +867,9 @@
   </si>
   <si>
     <t>Abono $180.866,63 el 27/04 y no lo pusimos pago. CHEQUEAR</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plan de pago de 11C: Consta de 10 Cuotas de $165.000 + expensas en curso </t>
   </si>
 </sst>
 </file>
@@ -2036,160 +2036,160 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="12" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="165" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="18" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="18" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="18" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="18" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="21" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="11" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="12" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="1" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="35" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="38" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="4">
     <cellStyle name="Hipervínculo" xfId="3" builtinId="8"/>
@@ -2579,12 +2579,12 @@
   <sheetData>
     <row r="1" spans="1:5" ht="18.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="2"/>
-      <c r="B1" s="236" t="s">
+      <c r="B1" s="244" t="s">
         <v>149</v>
       </c>
-      <c r="C1" s="236"/>
-      <c r="D1" s="236"/>
-      <c r="E1" s="237"/>
+      <c r="C1" s="244"/>
+      <c r="D1" s="244"/>
+      <c r="E1" s="245"/>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="3"/>
@@ -2597,12 +2597,12 @@
     </row>
     <row r="3" spans="1:5" ht="51.6" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A3" s="3"/>
-      <c r="B3" s="240" t="s">
-        <v>253</v>
-      </c>
-      <c r="C3" s="240"/>
-      <c r="D3" s="240"/>
-      <c r="E3" s="241"/>
+      <c r="B3" s="246" t="s">
+        <v>252</v>
+      </c>
+      <c r="C3" s="246"/>
+      <c r="D3" s="246"/>
+      <c r="E3" s="247"/>
     </row>
     <row r="4" spans="1:5" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A4" s="6" t="s">
@@ -2620,7 +2620,7 @@
         <v>150</v>
       </c>
       <c r="B5" s="8" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C5" s="10"/>
       <c r="D5" s="4" t="s">
@@ -2635,54 +2635,54 @@
       <c r="B6" s="8"/>
       <c r="C6" s="8"/>
       <c r="D6" s="8" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="E6" s="9"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B8" s="242" t="s">
-        <v>196</v>
-      </c>
-      <c r="C8" s="242"/>
+      <c r="B8" s="248" t="s">
+        <v>195</v>
+      </c>
+      <c r="C8" s="248"/>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B9" s="242"/>
-      <c r="C9" s="242"/>
+      <c r="B9" s="248"/>
+      <c r="C9" s="248"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="B10" s="242"/>
-      <c r="C10" s="242"/>
+      <c r="B10" s="248"/>
+      <c r="C10" s="248"/>
     </row>
     <row r="12" spans="1:5" hidden="1" x14ac:dyDescent="0.3"/>
     <row r="13" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="243" t="s">
+      <c r="A13" s="249" t="s">
         <v>105</v>
       </c>
-      <c r="B13" s="243"/>
-      <c r="C13" s="243"/>
-      <c r="D13" s="243"/>
-      <c r="E13" s="243"/>
+      <c r="B13" s="249"/>
+      <c r="C13" s="249"/>
+      <c r="D13" s="249"/>
+      <c r="E13" s="249"/>
     </row>
     <row r="14" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="243"/>
-      <c r="B14" s="243"/>
-      <c r="C14" s="243"/>
-      <c r="D14" s="243"/>
-      <c r="E14" s="243"/>
+      <c r="A14" s="249"/>
+      <c r="B14" s="249"/>
+      <c r="C14" s="249"/>
+      <c r="D14" s="249"/>
+      <c r="E14" s="249"/>
     </row>
     <row r="15" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="243"/>
-      <c r="B15" s="243"/>
-      <c r="C15" s="243"/>
-      <c r="D15" s="243"/>
-      <c r="E15" s="243"/>
+      <c r="A15" s="249"/>
+      <c r="B15" s="249"/>
+      <c r="C15" s="249"/>
+      <c r="D15" s="249"/>
+      <c r="E15" s="249"/>
     </row>
     <row r="16" spans="1:5" ht="53.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="243"/>
-      <c r="B16" s="243"/>
-      <c r="C16" s="243"/>
-      <c r="D16" s="243"/>
-      <c r="E16" s="243"/>
+      <c r="A16" s="249"/>
+      <c r="B16" s="249"/>
+      <c r="C16" s="249"/>
+      <c r="D16" s="249"/>
+      <c r="E16" s="249"/>
     </row>
     <row r="17" spans="1:8" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="18" spans="1:8" ht="15" hidden="1" thickBot="1" x14ac:dyDescent="0.35">
@@ -2708,10 +2708,10 @@
       <c r="E21" s="175"/>
     </row>
     <row r="22" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="238" t="s">
+      <c r="A22" s="241" t="s">
         <v>168</v>
       </c>
-      <c r="B22" s="239"/>
+      <c r="B22" s="242"/>
       <c r="C22" s="21"/>
       <c r="D22" s="137">
         <v>2038208.3</v>
@@ -2720,10 +2720,10 @@
       <c r="H22" s="22"/>
     </row>
     <row r="23" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="238" t="s">
+      <c r="A23" s="241" t="s">
         <v>169</v>
       </c>
-      <c r="B23" s="239"/>
+      <c r="B23" s="242"/>
       <c r="C23" s="21"/>
       <c r="D23" s="137">
         <v>-443310.3</v>
@@ -2732,10 +2732,10 @@
       <c r="H23" s="22"/>
     </row>
     <row r="24" spans="1:8" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="238" t="s">
+      <c r="A24" s="241" t="s">
         <v>1</v>
       </c>
-      <c r="B24" s="239"/>
+      <c r="B24" s="242"/>
       <c r="C24" s="21"/>
       <c r="D24" s="138">
         <v>0</v>
@@ -2757,7 +2757,7 @@
     </row>
     <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26" s="24" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="B26" s="24"/>
       <c r="C26" s="24"/>
@@ -2766,7 +2766,7 @@
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27" s="21" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B27" s="21"/>
       <c r="C27" s="21"/>
@@ -2774,12 +2774,12 @@
         <v>336000</v>
       </c>
       <c r="E27" s="191" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28" s="21" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B28" s="21"/>
       <c r="C28" s="21"/>
@@ -2793,19 +2793,19 @@
         <v>175</v>
       </c>
       <c r="B29" s="21" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C29" s="21"/>
       <c r="D29" s="38">
         <v>168000</v>
       </c>
       <c r="E29" s="191" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30" s="21" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B30" s="21"/>
       <c r="C30" s="21"/>
@@ -2839,7 +2839,7 @@
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" s="21" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="B33" s="94"/>
       <c r="C33" s="94"/>
@@ -2847,7 +2847,7 @@
         <v>12755.13</v>
       </c>
       <c r="E33" s="179" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
@@ -2860,7 +2860,7 @@
         <v>928582.19</v>
       </c>
       <c r="E34" s="179" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
@@ -2873,7 +2873,7 @@
         <v>178550.22</v>
       </c>
       <c r="E35" s="179" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.3">
@@ -2935,29 +2935,29 @@
       <c r="E40" s="180"/>
     </row>
     <row r="41" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="244" t="s">
-        <v>215</v>
-      </c>
-      <c r="B41" s="245"/>
+      <c r="A41" s="250" t="s">
+        <v>214</v>
+      </c>
+      <c r="B41" s="251"/>
       <c r="C41" s="29"/>
       <c r="D41" s="139">
         <v>7805</v>
       </c>
       <c r="E41" s="23" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="42" spans="1:5" ht="26.25" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="244" t="s">
-        <v>225</v>
-      </c>
-      <c r="B42" s="245"/>
+      <c r="A42" s="250" t="s">
+        <v>224</v>
+      </c>
+      <c r="B42" s="251"/>
       <c r="C42" s="29"/>
       <c r="D42" s="139">
         <v>214164</v>
       </c>
       <c r="E42" s="23" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
     </row>
     <row r="43" spans="1:5" x14ac:dyDescent="0.3">
@@ -2993,7 +2993,7 @@
         <v>998400.74</v>
       </c>
       <c r="E45" s="23" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="46" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
@@ -3008,12 +3008,12 @@
         <v>2467.0500000000002</v>
       </c>
       <c r="E46" s="23" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
     </row>
     <row r="47" spans="1:5" ht="14.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A47" s="32" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B47" s="32" t="s">
         <v>178</v>
@@ -3026,7 +3026,7 @@
     </row>
     <row r="48" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A48" s="32" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B48" s="34"/>
       <c r="C48" s="32"/>
@@ -3036,16 +3036,16 @@
       <c r="E48" s="23"/>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A49" s="244" t="s">
+      <c r="A49" s="250" t="s">
         <v>112</v>
       </c>
-      <c r="B49" s="245"/>
+      <c r="B49" s="251"/>
       <c r="C49" s="32"/>
       <c r="D49" s="33">
         <v>4517309.87</v>
       </c>
       <c r="E49" s="129" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
@@ -3077,167 +3077,167 @@
       <c r="E52" s="183"/>
     </row>
     <row r="53" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A53" s="238" t="s">
+      <c r="A53" s="241" t="s">
         <v>171</v>
       </c>
-      <c r="B53" s="239"/>
+      <c r="B53" s="242"/>
       <c r="C53" s="32"/>
       <c r="D53" s="33">
         <v>285000</v>
       </c>
       <c r="E53" s="37" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
     </row>
     <row r="54" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="238" t="s">
-        <v>226</v>
-      </c>
-      <c r="B54" s="239"/>
+      <c r="A54" s="241" t="s">
+        <v>225</v>
+      </c>
+      <c r="B54" s="242"/>
       <c r="C54" s="32"/>
       <c r="D54" s="33">
         <v>470000</v>
       </c>
       <c r="E54" s="126" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="55" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="238" t="s">
-        <v>236</v>
-      </c>
-      <c r="B55" s="239"/>
+      <c r="A55" s="241" t="s">
+        <v>235</v>
+      </c>
+      <c r="B55" s="242"/>
       <c r="C55" s="32"/>
       <c r="D55" s="33">
         <v>670000</v>
       </c>
       <c r="E55" s="126" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
     </row>
     <row r="56" spans="1:6" ht="33.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A56" s="238" t="s">
-        <v>204</v>
-      </c>
-      <c r="B56" s="239"/>
+      <c r="A56" s="241" t="s">
+        <v>203</v>
+      </c>
+      <c r="B56" s="242"/>
       <c r="C56" s="32"/>
       <c r="D56" s="33">
         <v>35000</v>
       </c>
       <c r="E56" s="126" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="57" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="238" t="s">
-        <v>202</v>
-      </c>
-      <c r="B57" s="239"/>
+      <c r="A57" s="241" t="s">
+        <v>201</v>
+      </c>
+      <c r="B57" s="242"/>
       <c r="C57" s="32"/>
       <c r="D57" s="33">
         <f>710000-380000</f>
         <v>330000</v>
       </c>
       <c r="E57" s="37" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="F57" s="53"/>
     </row>
     <row r="58" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="238" t="s">
-        <v>209</v>
-      </c>
-      <c r="B58" s="239"/>
+      <c r="A58" s="241" t="s">
+        <v>208</v>
+      </c>
+      <c r="B58" s="242"/>
       <c r="C58" s="32"/>
       <c r="D58" s="33">
         <v>35000</v>
       </c>
       <c r="E58" s="37" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F58" s="53"/>
     </row>
     <row r="59" spans="1:6" ht="33" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="238" t="s">
-        <v>221</v>
-      </c>
-      <c r="B59" s="239"/>
+      <c r="A59" s="241" t="s">
+        <v>220</v>
+      </c>
+      <c r="B59" s="242"/>
       <c r="C59" s="32"/>
       <c r="D59" s="33">
         <v>35000</v>
       </c>
       <c r="E59" s="37" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F59" s="53"/>
     </row>
     <row r="60" spans="1:6" ht="34.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A60" s="238" t="s">
-        <v>239</v>
-      </c>
-      <c r="B60" s="239"/>
+      <c r="A60" s="241" t="s">
+        <v>238</v>
+      </c>
+      <c r="B60" s="242"/>
       <c r="C60" s="32"/>
       <c r="D60" s="33">
         <v>320000</v>
       </c>
       <c r="E60" s="37" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F60" s="53"/>
     </row>
     <row r="61" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="238" t="s">
-        <v>205</v>
-      </c>
-      <c r="B61" s="239"/>
+      <c r="A61" s="241" t="s">
+        <v>204</v>
+      </c>
+      <c r="B61" s="242"/>
       <c r="C61" s="32"/>
       <c r="D61" s="33">
         <v>105000</v>
       </c>
       <c r="E61" s="190" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F61" s="53"/>
     </row>
     <row r="62" spans="1:6" ht="30" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="238" t="s">
-        <v>207</v>
-      </c>
-      <c r="B62" s="239"/>
+      <c r="A62" s="241" t="s">
+        <v>206</v>
+      </c>
+      <c r="B62" s="242"/>
       <c r="C62" s="32"/>
       <c r="D62" s="33">
         <v>150000</v>
       </c>
       <c r="E62" s="190" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="F62" s="53"/>
     </row>
     <row r="63" spans="1:6" ht="93.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="238" t="s">
-        <v>218</v>
-      </c>
-      <c r="B63" s="239"/>
+      <c r="A63" s="241" t="s">
+        <v>217</v>
+      </c>
+      <c r="B63" s="242"/>
       <c r="C63" s="32"/>
       <c r="D63" s="33">
         <v>2800000</v>
       </c>
       <c r="E63" s="190" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F63" s="53"/>
     </row>
     <row r="64" spans="1:6" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="238" t="s">
-        <v>234</v>
-      </c>
-      <c r="B64" s="239"/>
+      <c r="A64" s="241" t="s">
+        <v>233</v>
+      </c>
+      <c r="B64" s="242"/>
       <c r="C64" s="32"/>
       <c r="D64" s="33">
         <v>200000</v>
       </c>
       <c r="E64" s="190" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="F64" s="53"/>
     </row>
@@ -3257,7 +3257,7 @@
     </row>
     <row r="66" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A66" s="102" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="B66" s="20"/>
       <c r="C66" s="32"/>
@@ -3265,13 +3265,13 @@
         <v>31400</v>
       </c>
       <c r="E66" s="37" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F66" s="53"/>
     </row>
     <row r="67" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A67" s="102" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="B67" s="20"/>
       <c r="C67" s="32"/>
@@ -3279,13 +3279,13 @@
         <v>31400</v>
       </c>
       <c r="E67" s="37" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F67" s="53"/>
     </row>
     <row r="68" spans="1:6" ht="17.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A68" s="102" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="B68" s="20"/>
       <c r="C68" s="32"/>
@@ -3293,13 +3293,13 @@
         <v>31400</v>
       </c>
       <c r="E68" s="37" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="F68" s="53"/>
     </row>
     <row r="69" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A69" s="102" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="B69" s="20"/>
       <c r="C69" s="32"/>
@@ -3307,15 +3307,15 @@
         <v>141400</v>
       </c>
       <c r="E69" s="190" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="F69" s="53"/>
     </row>
     <row r="70" spans="1:6" ht="21.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A70" s="238" t="s">
-        <v>235</v>
-      </c>
-      <c r="B70" s="239"/>
+      <c r="A70" s="241" t="s">
+        <v>234</v>
+      </c>
+      <c r="B70" s="242"/>
       <c r="C70" s="32"/>
       <c r="D70" s="33">
         <v>0</v>
@@ -3345,21 +3345,21 @@
       <c r="E72" s="175"/>
     </row>
     <row r="73" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A73" s="238" t="s">
-        <v>220</v>
-      </c>
-      <c r="B73" s="239"/>
+      <c r="A73" s="241" t="s">
+        <v>219</v>
+      </c>
+      <c r="B73" s="242"/>
       <c r="C73" s="21"/>
       <c r="D73" s="140">
         <v>650000</v>
       </c>
       <c r="E73" s="176" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="74" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A74" s="19" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="B74" s="20"/>
       <c r="C74" s="21"/>
@@ -3367,7 +3367,7 @@
         <v>100000</v>
       </c>
       <c r="E74" s="176" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="75" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
@@ -3380,12 +3380,12 @@
         <v>250000</v>
       </c>
       <c r="E75" s="176" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
     </row>
     <row r="76" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A76" s="102" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="B76" s="20"/>
       <c r="C76" s="21"/>
@@ -3393,7 +3393,7 @@
         <v>45000</v>
       </c>
       <c r="E76" s="176" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
     </row>
     <row r="77" spans="1:6" x14ac:dyDescent="0.3">
@@ -3513,8 +3513,8 @@
       <c r="E89" s="63"/>
     </row>
     <row r="90" spans="1:8" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A90" s="238"/>
-      <c r="B90" s="239"/>
+      <c r="A90" s="241"/>
+      <c r="B90" s="242"/>
       <c r="C90" s="32"/>
       <c r="D90" s="38"/>
       <c r="E90" s="63"/>
@@ -3634,22 +3634,22 @@
       <c r="E105" s="51"/>
     </row>
     <row r="106" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A106" s="246" t="s">
+      <c r="A106" s="240" t="s">
         <v>182</v>
       </c>
-      <c r="B106" s="246"/>
+      <c r="B106" s="240"/>
       <c r="D106" s="51"/>
       <c r="E106" s="51"/>
     </row>
     <row r="107" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A107" s="246"/>
-      <c r="B107" s="246"/>
+      <c r="A107" s="240"/>
+      <c r="B107" s="240"/>
       <c r="D107" s="51"/>
       <c r="E107" s="51"/>
     </row>
     <row r="108" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A108" s="246"/>
-      <c r="B108" s="246"/>
+      <c r="A108" s="240"/>
+      <c r="B108" s="240"/>
       <c r="D108" s="51"/>
       <c r="E108" s="51"/>
     </row>
@@ -3658,22 +3658,22 @@
       <c r="E109" s="51"/>
     </row>
     <row r="110" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A110" s="246" t="s">
-        <v>183</v>
-      </c>
-      <c r="B110" s="246"/>
+      <c r="A110" s="240" t="s">
+        <v>277</v>
+      </c>
+      <c r="B110" s="240"/>
       <c r="D110" s="51"/>
       <c r="E110" s="51"/>
     </row>
     <row r="111" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A111" s="246"/>
-      <c r="B111" s="246"/>
+      <c r="A111" s="240"/>
+      <c r="B111" s="240"/>
       <c r="D111" s="51"/>
       <c r="E111" s="51"/>
     </row>
     <row r="112" spans="1:5" ht="15" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A112" s="246"/>
-      <c r="B112" s="246"/>
+      <c r="A112" s="240"/>
+      <c r="B112" s="240"/>
       <c r="D112" s="51"/>
       <c r="E112" s="51"/>
     </row>
@@ -3682,22 +3682,22 @@
       <c r="E113" s="51"/>
     </row>
     <row r="114" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A114" s="246" t="s">
-        <v>192</v>
-      </c>
-      <c r="B114" s="246"/>
+      <c r="A114" s="240" t="s">
+        <v>191</v>
+      </c>
+      <c r="B114" s="240"/>
       <c r="D114" s="51"/>
       <c r="E114" s="51"/>
     </row>
     <row r="115" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A115" s="246"/>
-      <c r="B115" s="246"/>
+      <c r="A115" s="240"/>
+      <c r="B115" s="240"/>
       <c r="D115" s="51"/>
       <c r="E115" s="51"/>
     </row>
     <row r="116" spans="1:5" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A116" s="246"/>
-      <c r="B116" s="246"/>
+      <c r="A116" s="240"/>
+      <c r="B116" s="240"/>
       <c r="D116" s="51"/>
       <c r="E116" s="51"/>
     </row>
@@ -3706,22 +3706,22 @@
       <c r="E117" s="51"/>
     </row>
     <row r="118" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A118" s="246" t="s">
-        <v>195</v>
-      </c>
-      <c r="B118" s="246"/>
+      <c r="A118" s="240" t="s">
+        <v>194</v>
+      </c>
+      <c r="B118" s="240"/>
       <c r="D118" s="51"/>
       <c r="E118" s="51"/>
     </row>
     <row r="119" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A119" s="246"/>
-      <c r="B119" s="246"/>
+      <c r="A119" s="240"/>
+      <c r="B119" s="240"/>
       <c r="D119" s="51"/>
       <c r="E119" s="51"/>
     </row>
     <row r="120" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A120" s="246"/>
-      <c r="B120" s="246"/>
+      <c r="A120" s="240"/>
+      <c r="B120" s="240"/>
       <c r="D120" s="51"/>
       <c r="E120" s="51"/>
     </row>
@@ -3730,22 +3730,22 @@
       <c r="E121" s="51"/>
     </row>
     <row r="122" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A122" s="246" t="s">
-        <v>194</v>
-      </c>
-      <c r="B122" s="246"/>
+      <c r="A122" s="240" t="s">
+        <v>193</v>
+      </c>
+      <c r="B122" s="240"/>
       <c r="D122" s="51"/>
       <c r="E122" s="51"/>
     </row>
     <row r="123" spans="1:5" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A123" s="246"/>
-      <c r="B123" s="246"/>
+      <c r="A123" s="240"/>
+      <c r="B123" s="240"/>
       <c r="D123" s="51"/>
       <c r="E123" s="51"/>
     </row>
     <row r="124" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A124" s="246"/>
-      <c r="B124" s="246"/>
+      <c r="A124" s="240"/>
+      <c r="B124" s="240"/>
       <c r="D124" s="51"/>
       <c r="E124" s="51"/>
     </row>
@@ -3762,7 +3762,7 @@
     </row>
     <row r="127" spans="1:5" s="71" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A127" s="209" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="B127" s="72">
         <v>-1034822.7662549634</v>
@@ -3808,7 +3808,7 @@
     </row>
     <row r="131" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A131" s="29" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="B131" s="167">
         <v>-195940.3</v>
@@ -3819,7 +3819,7 @@
     </row>
     <row r="132" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A132" s="29" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="B132" s="167">
         <v>-195940.3</v>
@@ -3830,7 +3830,7 @@
     </row>
     <row r="133" spans="1:13" ht="40.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A133" s="29" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B133" s="167">
         <v>-168835</v>
@@ -3853,20 +3853,20 @@
     </row>
     <row r="135" spans="1:13" ht="34.5" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="136" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A136" s="247" t="s">
+      <c r="A136" s="243" t="s">
         <v>127</v>
       </c>
-      <c r="B136" s="247"/>
-      <c r="C136" s="247"/>
+      <c r="B136" s="243"/>
+      <c r="C136" s="243"/>
     </row>
     <row r="137" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A137" s="247"/>
-      <c r="B137" s="247"/>
-      <c r="C137" s="247"/>
+      <c r="A137" s="243"/>
+      <c r="B137" s="243"/>
+      <c r="C137" s="243"/>
     </row>
     <row r="138" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A138" s="77" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B138" s="125">
         <v>130000</v>
@@ -3876,7 +3876,7 @@
     </row>
     <row r="139" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A139" s="168" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="B139" s="125">
         <v>87403</v>
@@ -3899,6 +3899,21 @@
     </row>
   </sheetData>
   <mergeCells count="31">
+    <mergeCell ref="B1:E1"/>
+    <mergeCell ref="A24:B24"/>
+    <mergeCell ref="A73:B73"/>
+    <mergeCell ref="B3:E3"/>
+    <mergeCell ref="B8:C10"/>
+    <mergeCell ref="A13:E16"/>
+    <mergeCell ref="A22:B22"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="A49:B49"/>
+    <mergeCell ref="A41:B41"/>
+    <mergeCell ref="A58:B58"/>
+    <mergeCell ref="A60:B60"/>
+    <mergeCell ref="A63:B63"/>
+    <mergeCell ref="A59:B59"/>
+    <mergeCell ref="A42:B42"/>
     <mergeCell ref="A114:B116"/>
     <mergeCell ref="A56:B56"/>
     <mergeCell ref="A136:C137"/>
@@ -3915,21 +3930,6 @@
     <mergeCell ref="A61:B61"/>
     <mergeCell ref="A62:B62"/>
     <mergeCell ref="A55:B55"/>
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="A24:B24"/>
-    <mergeCell ref="A73:B73"/>
-    <mergeCell ref="B3:E3"/>
-    <mergeCell ref="B8:C10"/>
-    <mergeCell ref="A13:E16"/>
-    <mergeCell ref="A22:B22"/>
-    <mergeCell ref="A23:B23"/>
-    <mergeCell ref="A49:B49"/>
-    <mergeCell ref="A41:B41"/>
-    <mergeCell ref="A58:B58"/>
-    <mergeCell ref="A60:B60"/>
-    <mergeCell ref="A63:B63"/>
-    <mergeCell ref="A59:B59"/>
-    <mergeCell ref="A42:B42"/>
   </mergeCells>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="5" scale="90" orientation="portrait" r:id="rId1"/>
@@ -3964,16 +3964,16 @@
       <c r="A1" s="103"/>
       <c r="B1" s="104"/>
       <c r="C1" s="104"/>
-      <c r="D1" s="248"/>
-      <c r="E1" s="248"/>
-      <c r="F1" s="248"/>
-      <c r="G1" s="248"/>
-      <c r="H1" s="248"/>
-      <c r="I1" s="248"/>
-      <c r="J1" s="248"/>
-      <c r="K1" s="248"/>
-      <c r="L1" s="248"/>
-      <c r="M1" s="248"/>
+      <c r="D1" s="257"/>
+      <c r="E1" s="257"/>
+      <c r="F1" s="257"/>
+      <c r="G1" s="257"/>
+      <c r="H1" s="257"/>
+      <c r="I1" s="257"/>
+      <c r="J1" s="257"/>
+      <c r="K1" s="257"/>
+      <c r="L1" s="257"/>
+      <c r="M1" s="257"/>
       <c r="N1" s="105"/>
     </row>
     <row r="2" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
@@ -3983,10 +3983,10 @@
       <c r="D2" s="108" t="s">
         <v>128</v>
       </c>
-      <c r="E2" s="272">
+      <c r="E2" s="279">
         <v>3000000</v>
       </c>
-      <c r="F2" s="272"/>
+      <c r="F2" s="279"/>
       <c r="G2" s="108"/>
       <c r="H2" s="108"/>
       <c r="I2" s="108" t="s">
@@ -4023,189 +4023,189 @@
       <c r="O3" s="83"/>
     </row>
     <row r="4" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="249" t="s">
+      <c r="A4" s="258" t="s">
         <v>165</v>
       </c>
-      <c r="B4" s="250"/>
-      <c r="C4" s="250"/>
-      <c r="D4" s="250"/>
-      <c r="E4" s="250"/>
-      <c r="F4" s="250"/>
-      <c r="G4" s="250"/>
-      <c r="H4" s="250"/>
-      <c r="I4" s="250"/>
-      <c r="J4" s="250"/>
-      <c r="K4" s="250"/>
-      <c r="L4" s="250"/>
-      <c r="M4" s="250"/>
-      <c r="N4" s="251"/>
+      <c r="B4" s="259"/>
+      <c r="C4" s="259"/>
+      <c r="D4" s="259"/>
+      <c r="E4" s="259"/>
+      <c r="F4" s="259"/>
+      <c r="G4" s="259"/>
+      <c r="H4" s="259"/>
+      <c r="I4" s="259"/>
+      <c r="J4" s="259"/>
+      <c r="K4" s="259"/>
+      <c r="L4" s="259"/>
+      <c r="M4" s="259"/>
+      <c r="N4" s="260"/>
       <c r="O4" s="83"/>
     </row>
     <row r="5" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="252"/>
-      <c r="B5" s="253"/>
-      <c r="C5" s="253"/>
-      <c r="D5" s="253"/>
-      <c r="E5" s="253"/>
-      <c r="F5" s="253"/>
-      <c r="G5" s="253"/>
-      <c r="H5" s="253"/>
-      <c r="I5" s="253"/>
-      <c r="J5" s="253"/>
-      <c r="K5" s="253"/>
-      <c r="L5" s="253"/>
-      <c r="M5" s="253"/>
-      <c r="N5" s="254"/>
+      <c r="A5" s="261"/>
+      <c r="B5" s="262"/>
+      <c r="C5" s="262"/>
+      <c r="D5" s="262"/>
+      <c r="E5" s="262"/>
+      <c r="F5" s="262"/>
+      <c r="G5" s="262"/>
+      <c r="H5" s="262"/>
+      <c r="I5" s="262"/>
+      <c r="J5" s="262"/>
+      <c r="K5" s="262"/>
+      <c r="L5" s="262"/>
+      <c r="M5" s="262"/>
+      <c r="N5" s="263"/>
       <c r="O5" s="83"/>
     </row>
     <row r="6" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="252"/>
-      <c r="B6" s="253"/>
-      <c r="C6" s="253"/>
-      <c r="D6" s="253"/>
-      <c r="E6" s="253"/>
-      <c r="F6" s="253"/>
-      <c r="G6" s="253"/>
-      <c r="H6" s="253"/>
-      <c r="I6" s="253"/>
-      <c r="J6" s="253"/>
-      <c r="K6" s="253"/>
-      <c r="L6" s="253"/>
-      <c r="M6" s="253"/>
-      <c r="N6" s="254"/>
+      <c r="A6" s="261"/>
+      <c r="B6" s="262"/>
+      <c r="C6" s="262"/>
+      <c r="D6" s="262"/>
+      <c r="E6" s="262"/>
+      <c r="F6" s="262"/>
+      <c r="G6" s="262"/>
+      <c r="H6" s="262"/>
+      <c r="I6" s="262"/>
+      <c r="J6" s="262"/>
+      <c r="K6" s="262"/>
+      <c r="L6" s="262"/>
+      <c r="M6" s="262"/>
+      <c r="N6" s="263"/>
       <c r="O6" s="83"/>
     </row>
     <row r="7" spans="1:16" ht="12.9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="252"/>
-      <c r="B7" s="253"/>
-      <c r="C7" s="253"/>
-      <c r="D7" s="253"/>
-      <c r="E7" s="253"/>
-      <c r="F7" s="253"/>
-      <c r="G7" s="253"/>
-      <c r="H7" s="253"/>
-      <c r="I7" s="253"/>
-      <c r="J7" s="253"/>
-      <c r="K7" s="253"/>
-      <c r="L7" s="253"/>
-      <c r="M7" s="253"/>
-      <c r="N7" s="254"/>
+      <c r="A7" s="261"/>
+      <c r="B7" s="262"/>
+      <c r="C7" s="262"/>
+      <c r="D7" s="262"/>
+      <c r="E7" s="262"/>
+      <c r="F7" s="262"/>
+      <c r="G7" s="262"/>
+      <c r="H7" s="262"/>
+      <c r="I7" s="262"/>
+      <c r="J7" s="262"/>
+      <c r="K7" s="262"/>
+      <c r="L7" s="262"/>
+      <c r="M7" s="262"/>
+      <c r="N7" s="263"/>
       <c r="O7" s="83"/>
     </row>
     <row r="8" spans="1:16" ht="192" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A8" s="255"/>
-      <c r="B8" s="256"/>
-      <c r="C8" s="256"/>
-      <c r="D8" s="256"/>
-      <c r="E8" s="256"/>
-      <c r="F8" s="256"/>
-      <c r="G8" s="256"/>
-      <c r="H8" s="256"/>
-      <c r="I8" s="256"/>
-      <c r="J8" s="256"/>
-      <c r="K8" s="256"/>
-      <c r="L8" s="256"/>
-      <c r="M8" s="256"/>
-      <c r="N8" s="257"/>
+      <c r="A8" s="264"/>
+      <c r="B8" s="265"/>
+      <c r="C8" s="265"/>
+      <c r="D8" s="265"/>
+      <c r="E8" s="265"/>
+      <c r="F8" s="265"/>
+      <c r="G8" s="265"/>
+      <c r="H8" s="265"/>
+      <c r="I8" s="265"/>
+      <c r="J8" s="265"/>
+      <c r="K8" s="265"/>
+      <c r="L8" s="265"/>
+      <c r="M8" s="265"/>
+      <c r="N8" s="266"/>
     </row>
     <row r="9" spans="1:16" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A9" s="266" t="s">
+      <c r="A9" s="273" t="s">
         <v>163</v>
       </c>
-      <c r="B9" s="267"/>
-      <c r="C9" s="267"/>
-      <c r="D9" s="267"/>
-      <c r="E9" s="267"/>
-      <c r="F9" s="267"/>
-      <c r="G9" s="267"/>
-      <c r="H9" s="267"/>
-      <c r="I9" s="267"/>
-      <c r="J9" s="267"/>
-      <c r="K9" s="267"/>
-      <c r="L9" s="267"/>
-      <c r="M9" s="267"/>
-      <c r="N9" s="268"/>
+      <c r="B9" s="274"/>
+      <c r="C9" s="274"/>
+      <c r="D9" s="274"/>
+      <c r="E9" s="274"/>
+      <c r="F9" s="274"/>
+      <c r="G9" s="274"/>
+      <c r="H9" s="274"/>
+      <c r="I9" s="274"/>
+      <c r="J9" s="274"/>
+      <c r="K9" s="274"/>
+      <c r="L9" s="274"/>
+      <c r="M9" s="274"/>
+      <c r="N9" s="275"/>
     </row>
     <row r="10" spans="1:16" ht="48" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A10" s="269" t="s">
+      <c r="A10" s="276" t="s">
         <v>164</v>
       </c>
-      <c r="B10" s="270"/>
-      <c r="C10" s="270"/>
-      <c r="D10" s="270"/>
-      <c r="E10" s="270"/>
-      <c r="F10" s="270"/>
-      <c r="G10" s="270"/>
-      <c r="H10" s="270"/>
-      <c r="I10" s="270"/>
-      <c r="J10" s="270"/>
-      <c r="K10" s="270"/>
-      <c r="L10" s="270"/>
-      <c r="M10" s="270"/>
-      <c r="N10" s="271"/>
+      <c r="B10" s="277"/>
+      <c r="C10" s="277"/>
+      <c r="D10" s="277"/>
+      <c r="E10" s="277"/>
+      <c r="F10" s="277"/>
+      <c r="G10" s="277"/>
+      <c r="H10" s="277"/>
+      <c r="I10" s="277"/>
+      <c r="J10" s="277"/>
+      <c r="K10" s="277"/>
+      <c r="L10" s="277"/>
+      <c r="M10" s="277"/>
+      <c r="N10" s="278"/>
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A11" s="258" t="s">
+      <c r="A11" s="267" t="s">
         <v>130</v>
       </c>
-      <c r="B11" s="260" t="s">
+      <c r="B11" s="269" t="s">
         <v>131</v>
       </c>
-      <c r="C11" s="260" t="s">
+      <c r="C11" s="269" t="s">
         <v>132</v>
       </c>
-      <c r="D11" s="260" t="s">
+      <c r="D11" s="269" t="s">
         <v>133</v>
       </c>
-      <c r="E11" s="262" t="s">
+      <c r="E11" s="252" t="s">
         <v>134</v>
       </c>
-      <c r="F11" s="260" t="s">
+      <c r="F11" s="269" t="s">
         <v>135</v>
       </c>
-      <c r="G11" s="264" t="s">
+      <c r="G11" s="271" t="s">
         <v>136</v>
       </c>
-      <c r="H11" s="262" t="s">
+      <c r="H11" s="252" t="s">
         <v>137</v>
       </c>
-      <c r="I11" s="262" t="s">
+      <c r="I11" s="252" t="s">
         <v>129</v>
       </c>
-      <c r="J11" s="262" t="s">
+      <c r="J11" s="252" t="s">
         <v>128</v>
       </c>
-      <c r="K11" s="273" t="s">
-        <v>185</v>
-      </c>
-      <c r="L11" s="275" t="s">
-        <v>193</v>
+      <c r="K11" s="280" t="s">
+        <v>184</v>
+      </c>
+      <c r="L11" s="282" t="s">
+        <v>192</v>
       </c>
       <c r="M11" s="164" t="s">
         <v>138</v>
       </c>
-      <c r="N11" s="277" t="s">
+      <c r="N11" s="254" t="s">
         <v>139</v>
       </c>
     </row>
     <row r="12" spans="1:16" ht="15.75" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="259"/>
-      <c r="B12" s="261"/>
-      <c r="C12" s="261"/>
-      <c r="D12" s="261"/>
-      <c r="E12" s="263"/>
-      <c r="F12" s="261"/>
-      <c r="G12" s="265"/>
-      <c r="H12" s="263"/>
-      <c r="I12" s="263"/>
-      <c r="J12" s="263"/>
-      <c r="K12" s="274"/>
-      <c r="L12" s="276"/>
+      <c r="A12" s="268"/>
+      <c r="B12" s="270"/>
+      <c r="C12" s="270"/>
+      <c r="D12" s="270"/>
+      <c r="E12" s="253"/>
+      <c r="F12" s="270"/>
+      <c r="G12" s="272"/>
+      <c r="H12" s="253"/>
+      <c r="I12" s="253"/>
+      <c r="J12" s="253"/>
+      <c r="K12" s="281"/>
+      <c r="L12" s="283"/>
       <c r="M12" s="165" t="str">
         <f>RESUMEN!B8</f>
         <v>VTO 15/05</v>
       </c>
-      <c r="N12" s="278"/>
+      <c r="N12" s="255"/>
     </row>
     <row r="13" spans="1:16" ht="17.100000000000001" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="148">
@@ -5185,7 +5185,7 @@
         <v>0.20000000000000004</v>
       </c>
       <c r="P32" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
     </row>
     <row r="33" spans="1:16" x14ac:dyDescent="0.3">
@@ -5243,7 +5243,7 @@
         <v>22</v>
       </c>
       <c r="B34" s="124" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="C34" s="90"/>
       <c r="D34" s="85">
@@ -5830,7 +5830,7 @@
         <v>0.33000000000000013</v>
       </c>
       <c r="P45" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
     </row>
     <row r="46" spans="1:16" x14ac:dyDescent="0.3">
@@ -6086,7 +6086,7 @@
         <v>0.38000000000000017</v>
       </c>
       <c r="P50" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
     </row>
     <row r="51" spans="1:16" x14ac:dyDescent="0.3">
@@ -6282,7 +6282,7 @@
         <v>0.42000000000000021</v>
       </c>
       <c r="P54" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
     </row>
     <row r="55" spans="1:16" x14ac:dyDescent="0.3">
@@ -6337,7 +6337,7 @@
         <v>0.43000000000000022</v>
       </c>
       <c r="P55" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
     </row>
     <row r="56" spans="1:16" x14ac:dyDescent="0.3">
@@ -6540,7 +6540,7 @@
         <v>0.47000000000000025</v>
       </c>
       <c r="P59" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
     </row>
     <row r="60" spans="1:16" x14ac:dyDescent="0.3">
@@ -7342,7 +7342,7 @@
         <v>0.63000000000000034</v>
       </c>
       <c r="P75" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
     </row>
     <row r="76" spans="1:16" x14ac:dyDescent="0.3">
@@ -8091,7 +8091,7 @@
         <v>0.78000000000000047</v>
       </c>
       <c r="P90" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
     </row>
     <row r="91" spans="1:16" x14ac:dyDescent="0.3">
@@ -9299,7 +9299,7 @@
         <v>103</v>
       </c>
       <c r="B115" s="124" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C115" s="123"/>
       <c r="D115" s="120">
@@ -9409,93 +9409,96 @@
     </row>
     <row r="119" spans="1:15" hidden="1" x14ac:dyDescent="0.3"/>
     <row r="120" spans="1:15" ht="9" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B120" s="279" t="s">
+      <c r="B120" s="256" t="s">
         <v>105</v>
       </c>
-      <c r="C120" s="279"/>
-      <c r="D120" s="279"/>
-      <c r="E120" s="279"/>
-      <c r="F120" s="279"/>
-      <c r="G120" s="279"/>
-      <c r="H120" s="279"/>
-      <c r="I120" s="279"/>
-      <c r="J120" s="279"/>
-      <c r="K120" s="279"/>
-      <c r="L120" s="279"/>
-      <c r="M120" s="279"/>
+      <c r="C120" s="256"/>
+      <c r="D120" s="256"/>
+      <c r="E120" s="256"/>
+      <c r="F120" s="256"/>
+      <c r="G120" s="256"/>
+      <c r="H120" s="256"/>
+      <c r="I120" s="256"/>
+      <c r="J120" s="256"/>
+      <c r="K120" s="256"/>
+      <c r="L120" s="256"/>
+      <c r="M120" s="256"/>
     </row>
     <row r="121" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B121" s="279"/>
-      <c r="C121" s="279"/>
-      <c r="D121" s="279"/>
-      <c r="E121" s="279"/>
-      <c r="F121" s="279"/>
-      <c r="G121" s="279"/>
-      <c r="H121" s="279"/>
-      <c r="I121" s="279"/>
-      <c r="J121" s="279"/>
-      <c r="K121" s="279"/>
-      <c r="L121" s="279"/>
-      <c r="M121" s="279"/>
+      <c r="B121" s="256"/>
+      <c r="C121" s="256"/>
+      <c r="D121" s="256"/>
+      <c r="E121" s="256"/>
+      <c r="F121" s="256"/>
+      <c r="G121" s="256"/>
+      <c r="H121" s="256"/>
+      <c r="I121" s="256"/>
+      <c r="J121" s="256"/>
+      <c r="K121" s="256"/>
+      <c r="L121" s="256"/>
+      <c r="M121" s="256"/>
     </row>
     <row r="122" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B122" s="279"/>
-      <c r="C122" s="279"/>
-      <c r="D122" s="279"/>
-      <c r="E122" s="279"/>
-      <c r="F122" s="279"/>
-      <c r="G122" s="279"/>
-      <c r="H122" s="279"/>
-      <c r="I122" s="279"/>
-      <c r="J122" s="279"/>
-      <c r="K122" s="279"/>
-      <c r="L122" s="279"/>
-      <c r="M122" s="279"/>
+      <c r="B122" s="256"/>
+      <c r="C122" s="256"/>
+      <c r="D122" s="256"/>
+      <c r="E122" s="256"/>
+      <c r="F122" s="256"/>
+      <c r="G122" s="256"/>
+      <c r="H122" s="256"/>
+      <c r="I122" s="256"/>
+      <c r="J122" s="256"/>
+      <c r="K122" s="256"/>
+      <c r="L122" s="256"/>
+      <c r="M122" s="256"/>
     </row>
     <row r="123" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B123" s="279"/>
-      <c r="C123" s="279"/>
-      <c r="D123" s="279"/>
-      <c r="E123" s="279"/>
-      <c r="F123" s="279"/>
-      <c r="G123" s="279"/>
-      <c r="H123" s="279"/>
-      <c r="I123" s="279"/>
-      <c r="J123" s="279"/>
-      <c r="K123" s="279"/>
-      <c r="L123" s="279"/>
-      <c r="M123" s="279"/>
+      <c r="B123" s="256"/>
+      <c r="C123" s="256"/>
+      <c r="D123" s="256"/>
+      <c r="E123" s="256"/>
+      <c r="F123" s="256"/>
+      <c r="G123" s="256"/>
+      <c r="H123" s="256"/>
+      <c r="I123" s="256"/>
+      <c r="J123" s="256"/>
+      <c r="K123" s="256"/>
+      <c r="L123" s="256"/>
+      <c r="M123" s="256"/>
     </row>
     <row r="124" spans="1:15" ht="12" hidden="1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B124" s="279"/>
-      <c r="C124" s="279"/>
-      <c r="D124" s="279"/>
-      <c r="E124" s="279"/>
-      <c r="F124" s="279"/>
-      <c r="G124" s="279"/>
-      <c r="H124" s="279"/>
-      <c r="I124" s="279"/>
-      <c r="J124" s="279"/>
-      <c r="K124" s="279"/>
-      <c r="L124" s="279"/>
-      <c r="M124" s="279"/>
+      <c r="B124" s="256"/>
+      <c r="C124" s="256"/>
+      <c r="D124" s="256"/>
+      <c r="E124" s="256"/>
+      <c r="F124" s="256"/>
+      <c r="G124" s="256"/>
+      <c r="H124" s="256"/>
+      <c r="I124" s="256"/>
+      <c r="J124" s="256"/>
+      <c r="K124" s="256"/>
+      <c r="L124" s="256"/>
+      <c r="M124" s="256"/>
     </row>
     <row r="125" spans="1:15" ht="67.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B125" s="279"/>
-      <c r="C125" s="279"/>
-      <c r="D125" s="279"/>
-      <c r="E125" s="279"/>
-      <c r="F125" s="279"/>
-      <c r="G125" s="279"/>
-      <c r="H125" s="279"/>
-      <c r="I125" s="279"/>
-      <c r="J125" s="279"/>
-      <c r="K125" s="279"/>
-      <c r="L125" s="279"/>
-      <c r="M125" s="279"/>
+      <c r="B125" s="256"/>
+      <c r="C125" s="256"/>
+      <c r="D125" s="256"/>
+      <c r="E125" s="256"/>
+      <c r="F125" s="256"/>
+      <c r="G125" s="256"/>
+      <c r="H125" s="256"/>
+      <c r="I125" s="256"/>
+      <c r="J125" s="256"/>
+      <c r="K125" s="256"/>
+      <c r="L125" s="256"/>
+      <c r="M125" s="256"/>
     </row>
   </sheetData>
   <mergeCells count="19">
+    <mergeCell ref="I11:I12"/>
+    <mergeCell ref="K11:K12"/>
+    <mergeCell ref="L11:L12"/>
     <mergeCell ref="J11:J12"/>
     <mergeCell ref="N11:N12"/>
     <mergeCell ref="B120:M125"/>
@@ -9512,9 +9515,6 @@
     <mergeCell ref="A9:N9"/>
     <mergeCell ref="A10:N10"/>
     <mergeCell ref="E2:F2"/>
-    <mergeCell ref="I11:I12"/>
-    <mergeCell ref="K11:K12"/>
-    <mergeCell ref="L11:L12"/>
   </mergeCells>
   <pageMargins left="0.23622047244094491" right="0.23622047244094491" top="0.74803149606299213" bottom="0.74803149606299213" header="0.31496062992125984" footer="0.31496062992125984"/>
   <pageSetup paperSize="3" scale="80" orientation="portrait" r:id="rId1"/>
@@ -9535,7 +9535,7 @@
     </row>
     <row r="4" spans="1:10" ht="13.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C4" s="215" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D4" s="216">
         <v>1</v>
@@ -9549,29 +9549,29 @@
     </row>
     <row r="5" spans="1:10" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
       <c r="C5" s="217" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D5" s="218"/>
       <c r="E5" t="s">
+        <v>257</v>
+      </c>
+      <c r="G5" t="s">
         <v>258</v>
       </c>
-      <c r="G5" t="s">
+      <c r="H5" t="s">
         <v>259</v>
-      </c>
-      <c r="H5" t="s">
-        <v>260</v>
       </c>
       <c r="J5" s="212"/>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C6" s="217" t="s">
+        <v>260</v>
+      </c>
+      <c r="D6" s="218" t="s">
         <v>261</v>
       </c>
-      <c r="D6" s="218" t="s">
+      <c r="E6" t="s">
         <v>262</v>
-      </c>
-      <c r="E6" t="s">
-        <v>263</v>
       </c>
       <c r="G6" t="s">
         <v>130</v>
@@ -9583,38 +9583,38 @@
     </row>
     <row r="7" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C7" s="50" t="s">
+        <v>263</v>
+      </c>
+      <c r="J7" s="212"/>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="C8" s="284" t="s">
         <v>264</v>
       </c>
-      <c r="J7" s="212"/>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="C8" s="280" t="s">
-        <v>265</v>
-      </c>
-      <c r="D8" s="281"/>
-      <c r="E8" s="281"/>
-      <c r="F8" s="281"/>
-      <c r="G8" s="281"/>
-      <c r="H8" s="281"/>
-      <c r="I8" s="281"/>
-      <c r="J8" s="282"/>
+      <c r="D8" s="285"/>
+      <c r="E8" s="285"/>
+      <c r="F8" s="285"/>
+      <c r="G8" s="285"/>
+      <c r="H8" s="285"/>
+      <c r="I8" s="285"/>
+      <c r="J8" s="286"/>
     </row>
     <row r="9" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C9" s="283"/>
-      <c r="D9" s="284"/>
-      <c r="E9" s="284"/>
-      <c r="F9" s="284"/>
-      <c r="G9" s="284"/>
-      <c r="H9" s="284"/>
-      <c r="I9" s="284"/>
-      <c r="J9" s="285"/>
+      <c r="C9" s="287"/>
+      <c r="D9" s="288"/>
+      <c r="E9" s="288"/>
+      <c r="F9" s="288"/>
+      <c r="G9" s="288"/>
+      <c r="H9" s="288"/>
+      <c r="I9" s="288"/>
+      <c r="J9" s="289"/>
     </row>
     <row r="11" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A11" s="219"/>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C12" s="220" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D12" s="221">
         <f>D4+1</f>
@@ -9629,70 +9629,70 @@
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C13" s="222" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D13" s="223"/>
       <c r="E13" t="s">
+        <v>257</v>
+      </c>
+      <c r="G13" t="s">
         <v>258</v>
       </c>
-      <c r="G13" t="s">
+      <c r="H13" t="s">
         <v>259</v>
-      </c>
-      <c r="H13" t="s">
-        <v>260</v>
       </c>
       <c r="J13" s="212"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="C14" s="222" t="s">
+        <v>260</v>
+      </c>
+      <c r="D14" s="223" t="s">
         <v>261</v>
       </c>
-      <c r="D14" s="223" t="s">
+      <c r="E14" t="s">
         <v>262</v>
-      </c>
-      <c r="E14" t="s">
-        <v>263</v>
       </c>
       <c r="G14" t="s">
         <v>130</v>
       </c>
       <c r="H14" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="J14" s="212"/>
     </row>
     <row r="15" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C15" s="50" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="J15" s="212"/>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="C16" s="280" t="s">
-        <v>266</v>
-      </c>
-      <c r="D16" s="281"/>
-      <c r="E16" s="281"/>
-      <c r="F16" s="281"/>
-      <c r="G16" s="281"/>
-      <c r="H16" s="281"/>
-      <c r="I16" s="281"/>
-      <c r="J16" s="282"/>
+      <c r="C16" s="284" t="s">
+        <v>265</v>
+      </c>
+      <c r="D16" s="285"/>
+      <c r="E16" s="285"/>
+      <c r="F16" s="285"/>
+      <c r="G16" s="285"/>
+      <c r="H16" s="285"/>
+      <c r="I16" s="285"/>
+      <c r="J16" s="286"/>
     </row>
     <row r="17" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C17" s="283"/>
-      <c r="D17" s="284"/>
-      <c r="E17" s="284"/>
-      <c r="F17" s="284"/>
-      <c r="G17" s="284"/>
-      <c r="H17" s="284"/>
-      <c r="I17" s="284"/>
-      <c r="J17" s="285"/>
+      <c r="C17" s="287"/>
+      <c r="D17" s="288"/>
+      <c r="E17" s="288"/>
+      <c r="F17" s="288"/>
+      <c r="G17" s="288"/>
+      <c r="H17" s="288"/>
+      <c r="I17" s="288"/>
+      <c r="J17" s="289"/>
     </row>
     <row r="19" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="20" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C20" s="227" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D20" s="228">
         <f>D12+1</f>
@@ -9707,73 +9707,73 @@
     </row>
     <row r="21" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C21" s="229" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D21" s="230"/>
       <c r="E21" t="s">
+        <v>257</v>
+      </c>
+      <c r="G21" t="s">
         <v>258</v>
       </c>
-      <c r="G21" t="s">
-        <v>259</v>
-      </c>
       <c r="H21" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="I21" s="226" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="J21" s="212"/>
     </row>
     <row r="22" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C22" s="229" t="s">
+        <v>260</v>
+      </c>
+      <c r="D22" s="230" t="s">
         <v>261</v>
       </c>
-      <c r="D22" s="230" t="s">
+      <c r="E22" t="s">
         <v>262</v>
-      </c>
-      <c r="E22" t="s">
-        <v>263</v>
       </c>
       <c r="G22" t="s">
         <v>130</v>
       </c>
       <c r="H22" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="J22" s="212"/>
     </row>
     <row r="23" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C23" s="50" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="J23" s="212"/>
     </row>
     <row r="24" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C24" s="280" t="s">
-        <v>270</v>
-      </c>
-      <c r="D24" s="281"/>
-      <c r="E24" s="281"/>
-      <c r="F24" s="281"/>
-      <c r="G24" s="281"/>
-      <c r="H24" s="281"/>
-      <c r="I24" s="281"/>
-      <c r="J24" s="282"/>
+      <c r="C24" s="284" t="s">
+        <v>269</v>
+      </c>
+      <c r="D24" s="285"/>
+      <c r="E24" s="285"/>
+      <c r="F24" s="285"/>
+      <c r="G24" s="285"/>
+      <c r="H24" s="285"/>
+      <c r="I24" s="285"/>
+      <c r="J24" s="286"/>
     </row>
     <row r="25" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C25" s="283"/>
-      <c r="D25" s="284"/>
-      <c r="E25" s="284"/>
-      <c r="F25" s="284"/>
-      <c r="G25" s="284"/>
-      <c r="H25" s="284"/>
-      <c r="I25" s="284"/>
-      <c r="J25" s="285"/>
+      <c r="C25" s="287"/>
+      <c r="D25" s="288"/>
+      <c r="E25" s="288"/>
+      <c r="F25" s="288"/>
+      <c r="G25" s="288"/>
+      <c r="H25" s="288"/>
+      <c r="I25" s="288"/>
+      <c r="J25" s="289"/>
     </row>
     <row r="27" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="28" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C28" s="233" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="D28" s="15">
         <f>D20+1</f>
@@ -9788,30 +9788,30 @@
     </row>
     <row r="29" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C29" s="234" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="D29" s="235"/>
       <c r="E29" t="s">
+        <v>257</v>
+      </c>
+      <c r="G29" t="s">
         <v>258</v>
       </c>
-      <c r="G29" t="s">
-        <v>259</v>
-      </c>
       <c r="H29" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="I29" s="226"/>
       <c r="J29" s="212"/>
     </row>
     <row r="30" spans="3:10" x14ac:dyDescent="0.3">
       <c r="C30" s="234" t="s">
+        <v>260</v>
+      </c>
+      <c r="D30" s="235" t="s">
         <v>261</v>
       </c>
-      <c r="D30" s="235" t="s">
+      <c r="E30" t="s">
         <v>262</v>
-      </c>
-      <c r="E30" t="s">
-        <v>263</v>
       </c>
       <c r="G30" t="s">
         <v>130</v>
@@ -9820,44 +9820,44 @@
         <v>46</v>
       </c>
       <c r="I30" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="J30" s="212"/>
     </row>
     <row r="31" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C31" s="50" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="J31" s="212"/>
     </row>
     <row r="32" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C32" s="280" t="s">
-        <v>273</v>
-      </c>
-      <c r="D32" s="281"/>
-      <c r="E32" s="281"/>
-      <c r="F32" s="281"/>
-      <c r="G32" s="281"/>
-      <c r="H32" s="281"/>
-      <c r="I32" s="281"/>
-      <c r="J32" s="282"/>
+      <c r="C32" s="284" t="s">
+        <v>272</v>
+      </c>
+      <c r="D32" s="285"/>
+      <c r="E32" s="285"/>
+      <c r="F32" s="285"/>
+      <c r="G32" s="285"/>
+      <c r="H32" s="285"/>
+      <c r="I32" s="285"/>
+      <c r="J32" s="286"/>
     </row>
     <row r="33" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C33" s="283"/>
-      <c r="D33" s="284"/>
-      <c r="E33" s="284"/>
-      <c r="F33" s="284"/>
-      <c r="G33" s="284"/>
-      <c r="H33" s="284"/>
-      <c r="I33" s="284"/>
-      <c r="J33" s="285"/>
+      <c r="C33" s="287"/>
+      <c r="D33" s="288"/>
+      <c r="E33" s="288"/>
+      <c r="F33" s="288"/>
+      <c r="G33" s="288"/>
+      <c r="H33" s="288"/>
+      <c r="I33" s="288"/>
+      <c r="J33" s="289"/>
     </row>
     <row r="35" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="36" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C36" s="286" t="s">
-        <v>256</v>
-      </c>
-      <c r="D36" s="287">
+      <c r="C36" s="236" t="s">
+        <v>255</v>
+      </c>
+      <c r="D36" s="237">
         <f>D28+1</f>
         <v>5</v>
       </c>
@@ -9869,67 +9869,67 @@
       <c r="J36" s="211"/>
     </row>
     <row r="37" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C37" s="288" t="s">
+      <c r="C37" s="238" t="s">
+        <v>256</v>
+      </c>
+      <c r="D37" s="239"/>
+      <c r="E37" t="s">
         <v>257</v>
       </c>
-      <c r="D37" s="289"/>
-      <c r="E37" t="s">
+      <c r="G37" t="s">
         <v>258</v>
       </c>
-      <c r="G37" t="s">
-        <v>259</v>
-      </c>
       <c r="H37" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="I37" s="226"/>
       <c r="J37" s="212"/>
     </row>
     <row r="38" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C38" s="288" t="s">
+      <c r="C38" s="238" t="s">
+        <v>260</v>
+      </c>
+      <c r="D38" s="239" t="s">
         <v>261</v>
       </c>
-      <c r="D38" s="289" t="s">
+      <c r="E38" t="s">
         <v>262</v>
-      </c>
-      <c r="E38" t="s">
-        <v>263</v>
       </c>
       <c r="G38" t="s">
         <v>130</v>
       </c>
       <c r="H38" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="J38" s="212"/>
     </row>
     <row r="39" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="C39" s="50" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="J39" s="212"/>
     </row>
     <row r="40" spans="3:10" x14ac:dyDescent="0.3">
-      <c r="C40" s="280" t="s">
-        <v>277</v>
-      </c>
-      <c r="D40" s="281"/>
-      <c r="E40" s="281"/>
-      <c r="F40" s="281"/>
-      <c r="G40" s="281"/>
-      <c r="H40" s="281"/>
-      <c r="I40" s="281"/>
-      <c r="J40" s="282"/>
+      <c r="C40" s="284" t="s">
+        <v>276</v>
+      </c>
+      <c r="D40" s="285"/>
+      <c r="E40" s="285"/>
+      <c r="F40" s="285"/>
+      <c r="G40" s="285"/>
+      <c r="H40" s="285"/>
+      <c r="I40" s="285"/>
+      <c r="J40" s="286"/>
     </row>
     <row r="41" spans="3:10" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C41" s="283"/>
-      <c r="D41" s="284"/>
-      <c r="E41" s="284"/>
-      <c r="F41" s="284"/>
-      <c r="G41" s="284"/>
-      <c r="H41" s="284"/>
-      <c r="I41" s="284"/>
-      <c r="J41" s="285"/>
+      <c r="C41" s="287"/>
+      <c r="D41" s="288"/>
+      <c r="E41" s="288"/>
+      <c r="F41" s="288"/>
+      <c r="G41" s="288"/>
+      <c r="H41" s="288"/>
+      <c r="I41" s="288"/>
+      <c r="J41" s="289"/>
     </row>
   </sheetData>
   <mergeCells count="5">
